--- a/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
+++ b/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
@@ -877,7 +877,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7a1c402</t>
+          <t>56e7134</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z2" s="22" t="inlineStr">
         <is>
-          <t>Commit 5ce7575 (migración V2 JWT). También AuthMiddleware.php, Jwt.php y AuthContext.jsx. Historial Git agregado (no un commit por prompt). Sin prueba unitaria de login.</t>
+          <t>Origen JWT: 5ce7575. Claim nombre_completo en login: 4e08b9e [I-001]. También AuthMiddleware.php, Jwt.php y AuthContext.jsx. Sin prueba unitaria de login.</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="U3" s="27" t="inlineStr">
         <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/9950f99/src/features/configuracion/components/ConfiguracionPage.jsx</t>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/ConfiguracionPage.jsx</t>
         </is>
       </c>
       <c r="V3" s="27" t="inlineStr">
         <is>
-          <t>9950f99</t>
+          <t>4e08b9e</t>
         </is>
       </c>
       <c r="W3" s="26" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z3" s="26" t="inlineStr">
         <is>
-          <t>Commit 9950f99 (estructura inicial; incremento 5 v0.5.0 via en ese lote). API: AreaController.php y UsuarioController.php.</t>
+          <t>SHA vigente: 4e08b9e [I-001] (nombre completo y UI de usuarios). Origen del módulo: 9950f99. API: AreaController.php y UsuarioController.php.</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U4" s="25" t="inlineStr">
         <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/9950f99/backend/api/v2/controllers/EquipoController.php</t>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/EquipoController.php</t>
         </is>
       </c>
       <c r="V4" s="25" t="inlineStr">
         <is>
-          <t>9950f99</t>
+          <t>f086a63</t>
         </is>
       </c>
       <c r="W4" s="22" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z4" s="22" t="inlineStr">
         <is>
-          <t>Commit 9950f99 (origen del CRUD). Evoluciones posteriores en 06d75b1 y 1c63dbe. Test unitario solo de tipo de equipo (Vitest).</t>
+          <t>SHA vigente: f086a63 [I-001] (evaluación, PDF y esquema). Origen del CRUD: 9950f99. Test unitario solo de tipo de equipo (Vitest).</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="U5" s="27" t="inlineStr">
         <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/9950f99/backend/api/v2/controllers/FichaTecnicaController.php</t>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/FichaTecnicaController.php</t>
         </is>
       </c>
       <c r="V5" s="27" t="inlineStr">
         <is>
-          <t>9950f99</t>
+          <t>f086a63</t>
         </is>
       </c>
       <c r="W5" s="26" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z5" s="26" t="inlineStr">
         <is>
-          <t>Commit 9950f99 (origen). UI: FichaTecnicaPage.jsx y FichaTecnicaPanel.jsx. Bloque predictivo en 8b20337 (v0.9.0).</t>
+          <t>SHA vigente: f086a63 [I-001] (FichaTecnicaController y panel). Origen: 9950f99. Bloque predictivo: 8b20337 (v0.9.0).</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="U9" s="27" t="inlineStr">
         <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/backend/api/v2/controllers/ReporteController.php</t>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/ReporteController.php</t>
         </is>
       </c>
       <c r="V9" s="27" t="inlineStr">
         <is>
-          <t>5ce7575</t>
+          <t>f086a63</t>
         </is>
       </c>
       <c r="W9" s="26" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z9" s="26" t="inlineStr">
         <is>
-          <t>Commit 5ce7575 (descarga PDF con JWT). Origen del controlador: 9950f99. Sin prueba unitaria del PDF.</t>
+          <t>SHA vigente: f086a63 [I-001] (ReporteController y downloadPdf). JWT en blob: 5ce7575. Origen: 9950f99.</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="K2" s="25" t="inlineStr">
         <is>
-          <t>prompts/03_implementacion/I-001_api_auth_inventario_v1.md · Código: 9950f99 (origen), 5ce7575 (JWT/dashboard). Ver columna Commit de F-001 a F-006 y F-008.</t>
+          <t>prompts/03_implementacion/I-001_api_auth_inventario_v1.md · Vigente: f086a63 (inventario/ficha/PDF), 4e08b9e (configuración). Origen: 9950f99, JWT: 5ce7575.</t>
         </is>
       </c>
     </row>

--- a/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
+++ b/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad los IDs siguen el repositorio prompts/: I-001 (API V2 e inventario) e I-002 (microservicio ML).</t>
+          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad los IDs vigentes son I-002…I-009 (una fila por función F-001…F-008 en Prompts Detallados).</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Al mantener el sistema: 1) registra o reutiliza un prompt en prompts/; 2) implementa el cambio; 3) haz commit con el ID del prompt en el mensaje, p. ej. feat(inventario): validar código [I-001]; 4) actualiza SHA, Link GitHub y N.º de iteraciones en esta matriz.</t>
+          <t>Al mantener el sistema: 1) registra o reutiliza un prompt en prompts/; 2) implementa el cambio; 3) haz commit con el ID del prompt en el mensaje, p. ej. feat(inventario): validar código [I-002]; 4) actualiza SHA, Link GitHub y N.º de iteraciones en esta matriz.</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <row r="20" ht="42" customHeight="1" s="14">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Explica que las 5 columnas DevOps operan bajo Amaro et al. (2025); las de prompt versionado bajo Jiang et al. (2025); y que la trazabilidad de mantenimiento es prompt → commit GitHub → archivo (síntesis original del caso Sigemad). Limitación: el historial Git anterior a esta matriz es agregado (pocos commits grandes), no un SHA por cada prompt; I-001 e I-002 se documentaron de forma retrospectiva (metodologia.md §7). A partir de este registro, cada cambio asistido por IA debe dejar SHA propio.</t>
+          <t>Explica que las 5 columnas DevOps operan bajo Amaro et al. (2025); las de prompt versionado bajo Jiang et al. (2025); y que la trazabilidad de mantenimiento es prompt → commit GitHub → archivo (síntesis original del caso Sigemad). Limitación: el historial Git anterior a esta matriz es agregado (pocos commits grandes), no un SHA por cada prompt; los I-00N se documentaron de forma retrospectiva (metodologia.md). A partir de este registro, cada cambio asistido por IA debe dejar SHA propio.</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>tipo(modulo): mensaje [I-001]  — ejemplo: feat(inventario): filtro por área [I-001]</t>
+          <t>tipo(modulo): mensaje [I-002]  — ejemplo: feat(inventario): filtro por área [I-002]</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-006</t>
         </is>
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>CoT guiado</t>
         </is>
       </c>
       <c r="N2" s="22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z2" s="22" t="inlineStr">
         <is>
-          <t>Origen JWT: 5ce7575. Claim nombre_completo en login: 4e08b9e [I-001]. También AuthMiddleware.php, Jwt.php y AuthContext.jsx. Sin prueba unitaria de login.</t>
+          <t>Origen JWT: 5ce7575 [I-006]. RBAC en servidor: I-009. También AuthMiddleware.php, Jwt.php y AuthContext.jsx.</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="L3" s="27" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-005</t>
         </is>
       </c>
       <c r="M3" s="26" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>Few-shot</t>
         </is>
       </c>
       <c r="N3" s="26" t="inlineStr">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="O3" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="26" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z3" s="26" t="inlineStr">
         <is>
-          <t>SHA vigente: 4e08b9e [I-001] (nombre completo y UI de usuarios). Origen del módulo: 9950f99. API: AreaController.php y UsuarioController.php.</t>
+          <t>SHA vigente: 4e08b9e [I-005]. requireRole Administrador: I-009. API: AreaController.php y UsuarioController.php.</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-002</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>Few-shot</t>
         </is>
       </c>
       <c r="N4" s="22" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z4" s="22" t="inlineStr">
         <is>
-          <t>SHA vigente: f086a63 [I-001] (evaluación, PDF y esquema). Origen del CRUD: 9950f99. Test unitario solo de tipo de equipo (Vitest).</t>
+          <t>SHA vigente: f086a63 [I-002]. Telemetría: I-008. Plantilla Excel: I-009. Test unitario de tipo de equipo (Vitest).</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="L5" s="27" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-003</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>Few-shot</t>
         </is>
       </c>
       <c r="N5" s="26" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z5" s="26" t="inlineStr">
         <is>
-          <t>SHA vigente: f086a63 [I-001] (FichaTecnicaController y panel). Origen: 9950f99. Bloque predictivo: 8b20337 (v0.9.0).</t>
+          <t>SHA vigente: f086a63 [I-003]. Bloque predictivo en ficha: 8b20337 [I-008].</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-003</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>Few-shot</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z6" s="22" t="inlineStr">
         <is>
-          <t>Commit 8b20337 (v0.9.0 telemetría y correctivo estructurado). Origen del módulo: 9950f99. PHPUnit: sync de telemetría.</t>
+          <t>SHA de timeline/categoría: 8b20337 [I-003]. Sync de telemetría: I-008. PHPUnit: sync de telemetría.</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="L7" s="27" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-006</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>CoT guiado</t>
         </is>
       </c>
       <c r="N7" s="26" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="Z7" s="26" t="inlineStr">
         <is>
-          <t>Commit 5ce7575 (dashboard de métricas + JWT). Alertas ML y consulta: 8b20337. PHPUnit cubre filtros de consulta. Monitoring de software = No.</t>
+          <t>Commit 5ce7575 [I-006] (dashboard de métricas + JWT). Alertas ML: I-007. Consulta tipo_otro: I-008.</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="L8" s="25" t="inlineStr">
         <is>
-          <t>I-002</t>
+          <t>I-007</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>CoT guiado</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="O8" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="22" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z8" s="22" t="inlineStr">
         <is>
-          <t>Commit e9a0965 (FastAPI). Proxy PHP y cierre v0.9.0: 06d75b1 / 8b20337. pytest: test_features.py y test_ml_schemas.py. ML opcional.</t>
+          <t>Commit e9a0965 [I-007] (FastAPI). Telemetría/ficha predictiva: I-008. pytest: test_features.py y test_ml_schemas.py.</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="L9" s="27" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-004</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>Zero-shot + few-shot</t>
         </is>
       </c>
       <c r="N9" s="26" t="inlineStr">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="O9" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="26" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z9" s="26" t="inlineStr">
         <is>
-          <t>SHA vigente: f086a63 [I-001] (ReporteController y downloadPdf). JWT en blob: 5ce7575. Origen: 9950f99.</t>
+          <t>SHA vigente: f086a63 [I-004]. Descarga con JWT (blob): 5ce7575 [I-006].</t>
         </is>
       </c>
     </row>
@@ -2178,18 +2178,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="10" customWidth="1" style="14" min="1" max="1"/>
-    <col width="14" customWidth="1" style="14" min="2" max="2"/>
-    <col width="60" customWidth="1" style="14" min="3" max="3"/>
-    <col width="16" customWidth="1" style="14" min="4" max="4"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="28" customWidth="1" style="14" min="2" max="2"/>
+    <col width="72" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18" customWidth="1" style="14" min="4" max="4"/>
     <col width="12" customWidth="1" style="14" min="5" max="6"/>
     <col width="28" customWidth="1" style="14" min="7" max="7"/>
     <col width="12" customWidth="1" style="14" min="8" max="9"/>
     <col width="24" customWidth="1" style="14" min="10" max="10"/>
-    <col width="14" customWidth="1" style="14" min="11" max="11"/>
+    <col width="16" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="14">
@@ -2252,22 +2252,22 @@
     <row r="2" ht="90" customHeight="1" s="14">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>I-001</t>
+          <t>I-006</t>
         </is>
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>F-001 a F-006, F-008</t>
+          <t>F-001</t>
         </is>
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>Actúa como un desarrollador senior PHP/React. Contexto: API en backend/api/v2, frontend organizado por features, JWT y RBAC (Administrador, Técnico, Practicante). Implementa autenticación, CRUD de equipos, fichas técnicas, mantenimientos, áreas, usuarios, dashboard y reportes PDF. Restricciones: respuestas JSON estándar {success, data, message}; middleware JWT en todas las rutas salvo /auth; código patrimonial de 12 dígitos. No inventar integraciones SIGA/SIAF ni portal ciudadano.</t>
+          <t>Actúa como desarrollador senior PHP (firebase/php-jwt) y React (AuthContext, Axios). Contexto: API v2 y módulos INV/MNT/CFG sin JWT obligatorio; ADR-001 exige Bearer salvo /auth. Objetivo: login, sesión persistente y protección de /v2/* y de la API. Tarea: POST /auth/login → JWT; AuthMiddleware::requireAuth excepto /auth; Login.jsx, AuthContext, PrivateRoute; interceptor Axios; 401 → login; Navbar con Salir. Restricciones: secret solo en config no versionada; no revelar si el usuario existe; no FastAPI. Criterios: login correcto → /v2/dashboard; F5 mantiene sesión; sin token API 401.</t>
         </is>
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>CoT guiado</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G2" s="22" t="inlineStr">
         <is>
-          <t>Registro retrospectivo en prompts/; aprobado en primera versión documentada (incrementos 1–6, v0.1.0–0.6.0).</t>
+          <t>N/A — aprobado en primera versión documentada. El endurecimiento de roles es I-009.</t>
         </is>
       </c>
       <c r="H2" s="22" t="inlineStr">
@@ -2295,84 +2295,532 @@
       </c>
       <c r="J2" s="22" t="inlineStr">
         <is>
-          <t>API V2 + features React de auth, configuración, inventario, ficha, mantenimiento, dashboard y reportes</t>
+          <t>Login JWT funcional (AuthContext, PrivateRoute, middleware)</t>
         </is>
       </c>
       <c r="K2" s="25" t="inlineStr">
         <is>
-          <t>prompts/03_implementacion/I-001_api_auth_inventario_v1.md · Vigente: f086a63 (inventario/ficha/PDF), 4e08b9e (configuración). Origen: 9950f99, JWT: 5ce7575.</t>
+          <t>5ce7575</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" s="14">
       <c r="A3" s="27" t="inlineStr">
         <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP/React. Contexto: áreas y responsables no deben estar hardcodeados en EquipoForm; tablas v2_areas y v2_usuarios existen; ruta /v2/configuracion; roles Administrador, Tecnico, Practicante. Objetivo: CRUD de áreas y alta/listado de personal. Tarea: modelos PDO; password_hash BCRYPT; rutas /areas y /usuarios; ConfiguracionPage (pestañas); EquipoForm consume áreas desde API. Restricciones: no MD5; no requireRole en este incremento (deuda → I-009). Criterios: crear un área y verla en EquipoForm; usuario con hash en BD.</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>La API de usuarios quedó solo autenticada. I-009 añade requireRole Administrador.</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>Áreas y personal funcionales; EquipoForm dinámico</t>
+        </is>
+      </c>
+      <c r="K3" s="27" t="inlineStr">
+        <is>
+          <t>4e08b9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1" s="14">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
           <t>I-002</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP/React sobre el esqueleto I-001. Contexto: v2_equipos ya existe; CRUD mínimo ML-ready (ram_gb, almacenamiento_gb, fechas); código patrimonial de 12 dígitos; tabla + modal Tailwind. Objetivo: listado y alta vía /api/v2/equipos y src/features/inventario, sin fichas ni PDF. Tarea: Equipo.php (getAll, create); EquipoController JSON {success, data, message}; InventarioPage y EquipoForm. Restricciones: 12 dígitos únicos; no texto “8 GB”; no FastAPI. Criterios: POST persiste y GET lista; el form rechaza código ≠ 12.</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>N/A — no confundir con I-002-ML histórico (ahora I-007).</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>CRUD de equipos con código de 12 dígitos y RAM numérica</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1" s="14">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP/React; replica el patrón I-002. Contexto: equipos ya se listan; hace falta consultar/editar ficha técnica del equipo. Tarea: modelo/controlador/ruta de fichas; GET por id y por código patrimonial; acceso desde inventario (modal o /v2/ficha-tecnica). Restricciones: no PDF (I-004); no bloque ML (I-008). Criterios: GET ficha existente o vacío controlado (no 500).</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>N/A — evaluación predictiva en ficha es I-008.</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>API y UI de ficha técnica por id o código</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="14">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP/React; patrón I-002. Contexto: historial de intervenciones con categoria_falla_id del catálogo v2_categorias_falla; no texto libre como verdad de la falla. Objetivo: registrar y listar mantenimientos. Tarea: Mantenimiento.php getAll (JOIN categoría y técnico) y create; timeline + modal; select de categoría. Restricciones: categoría obligatoria en correctivo; no telemetría (I-008); no ML (I-007). Criterios: POST liga equipo_id; timeline muestra fecha, tipo y categoría nombrada.</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>N/A — sync de telemetría es I-008.</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>Timeline y alta estructurada de mantenimientos</t>
+        </is>
+      </c>
+      <c r="K6" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1" s="14">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP/React (mismo incremento 0.6.0 que F-001). Objetivo: métricas operativas en GET /api/v2/dashboard y UI DashboardPage (conteos, no ML). Tarea: DashboardController + DashboardPage; no badges de riesgo (I-007); no panel de consulta por etiquetas (I-008). Restricciones: no llamar a :8000. Criterios: dashboard muestra conteos persistidos tras login.</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>N/A — consulta tipo_otro es I-008; alertas ML son I-007.</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>Dashboard de métricas operativas funcional</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1" s="14">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>F-007</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>Actúa como ingeniero ML y backend. Contexto: dataset estructurado desde inventario y mantenimientos. Modelo de riesgo por equipo (Random Forest) y sugerencia de categoría de falla. Implementa microservicio FastAPI (entrenamiento e inferencia), tabla v2_predicciones_ml, proxy PHP autenticado /api/v2/ml/*, badges de riesgo en inventario y alertas en dashboard. Restricciones: PHP es el único cliente del puerto 8000; si FastAPI no responde, el resto del sistema continúa (degradación controlada).</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Zero-shot</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como ingeniero de ML aplicado y backend PHP. Contexto: datos estructurados (I-002, I-003); JWT (I-006); FastAPI en :8000; PHP único cliente; Hostinger sin Python. Objetivo: riesgo por equipo, sugerencia de categoría, proxy JWT y UI degradable. Tarea: dataset sintético ~200; Random Forest; /health, /predict/riesgo, batch, /predict/categoria, /train; tabla v2_predicciones_ml; proxy /api/v2/ml/*; badges. Restricciones: batch JSON {} no []; si FastAPI cae, inventario y login siguen. Criterios: /health OK; 401 sin token; UI sin crash con uvicorn down.</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F3" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="26" t="inlineStr">
-        <is>
-          <t>Registro retrospectivo en prompts/; aprobado en incrementos 6–7 (v0.7.0–0.9.0).</t>
-        </is>
-      </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="F8" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Batch enviaba []; curl devolvía HTTP 503 con cuerpo OK.</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr">
-        <is>
-          <t>FastAPI + proxy PHP + UI de riesgo y ficha predictiva; pytest de features y schemas</t>
-        </is>
-      </c>
-      <c r="K3" s="27" t="inlineStr">
-        <is>
-          <t>prompts/03_implementacion/I-002_microservicio_ml_v1.md · Código: e9a0965 (FastAPI), 8b20337 (cierre v0.9.0). Ver F-007.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="101.5" customHeight="1" s="14"/>
-    <row r="5" ht="101.5" customHeight="1" s="14"/>
-    <row r="6" ht="101.5" customHeight="1" s="14"/>
-    <row r="7" ht="101.5" customHeight="1" s="14"/>
-    <row r="8" ht="116" customHeight="1" s="14"/>
-    <row r="9" ht="116" customHeight="1" s="14"/>
-    <row r="10" ht="101.5" customHeight="1" s="14"/>
-    <row r="11" ht="116" customHeight="1" s="14"/>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>FastAPI + proxy PHP + badges; degradación controlada</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1" s="14">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP (dompdf) y React. Contexto: inventario y ficha ya existen. Objetivo: GET /api/v2/reportes/equipo/{id} genera PDF; InventarioPage filtra en cliente y ofrece descargar ficha. Tarea: Composer dompdf; ReporteController HTML→PDF; botón en la fila. Restricciones: PDF binario, no base64; no reportes de mantenimiento en este incremento. Criterios: PDF muestra código patrimonial; filtro de texto reduce filas.</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Zero-shot + few-shot</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>window.open sin token; I-006 cambia la descarga a blob + Authorization.</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>PDF de ficha y filtros de inventario funcionales</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1" s="14">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>I-008</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>F-003, F-005, F-006, F-007</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador PHP/React e ingeniero de datos ML. Contexto: ML 0.7.0 ya opera (I-007). Ampliar v2_equipos y v2_fichas_mantenimiento con telemetría y contexto de intervención; syncTelemetria al registrar mantenimiento; consulta de dashboard; bloque predictivo en ficha. No agente WMI ni DELETE de equipos. Criterios: migrate sobre BD 0.7.0 sin pérdida; POST mantenimiento actualiza snapshot; ficha muestra score si ML está arriba.</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>I-007 no incluía telemetría; D-005 pidió evolución por fases (0.8.0 y 0.9.0).</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>Telemetría, sync, ficha predictiva y consulta de equipos</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1" s="14">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>I-009</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>F-001, F-002, F-003</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior de API PHP y React. Contexto: 0.9.1; JWT existe; un Técnico puede mutar /usuarios; plantilla Excel desalinea numero_serie/area por falta de color. Objetivo: requireRole Administrador en escritura de usuarios; no autoeliminación ni borrar el último admin; RoleRoute en Configuración; fila ejemplo Excel alineada. Criterios: Técnico en POST /usuarios → 403.</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>I-005 no puso autorización en servidor (deuda de RBAC).</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>requireRole en /usuarios y plantilla Excel alineada</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2604,7 +3052,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Identificador del prompt que generó o modificó el módulo (I-001, I-002). En la matriz es un hipervínculo al markdown en GitHub (prompts/).</t>
+          <t>Identificador del prompt vigente (I-002…I-009). Una fila por función F-001…F-008 en Prompts Detallados. Hipervínculo al markdown en GitHub (prompts/).</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">

--- a/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
+++ b/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario de Columnas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Matriz Consolidada'!$A$1:$Z$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Matriz Consolidada'!$A$1:$Z$10</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -130,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -251,16 +251,16 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -685,7 +685,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad los IDs vigentes son I-002…I-009 (una fila por función F-001…F-008 en Prompts Detallados).</t>
+          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad los IDs vigentes son I-002…I-017 (una fila por función F-001…F-009 en Prompts Detallados, más refinamientos I-008…I-017).</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Busca en 'Matriz Consolidada' por 'Feature/Módulo' (auth, inventario, ficha, mantenimiento, dashboard, ml, reportes, configuracion) o 'ID Función' (F-001 a F-008).</t>
+          <t>Busca en 'Matriz Consolidada' por 'Feature/Módulo' (auth, inventario, ficha, mantenimiento, dashboard, ml, reportes, configuracion, cronograma) o 'ID Función' (F-001 a F-009).</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Observa las 5 columnas DevOps (Amaro): verde = Sí implementado, amarillo = Parcial, rojo = No implementado. En este caso: Control de Versiones = Sí (Git); CI y CD = No (no hay pipeline GitHub Actions ni despliegue automático; Hostinger es manual); Test Automation = Parcial en inventario, mantenimiento, dashboard y ML; Continuous Monitoring = No.</t>
+          <t>Observa las 5 columnas DevOps (Amaro): verde = Sí implementado, amarillo = Parcial, rojo = No implementado. En este caso: Control de Versiones = Sí (Git); CI y CD = No (no hay pipeline GitHub Actions ni despliegue automático; Hostinger es manual); Test Automation = Parcial en auth, configuración, inventario, mantenimiento, dashboard, ML, reportes (PDF cronograma) y cronograma; Continuous Monitoring = No.</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56e7134</t>
+          <t>3394712</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>B3 es el HEAD de origin/main al publicar la matriz. Cada fila de 'Matriz Consolidada' tiene su propio SHA en la columna Commit (hipervínculo al diff). Los prompts se leen en rama main: prompts/03_implementacion/.</t>
+          <t>B3 es el HEAD de origin/main al regenerar la matriz. Cada fila de Matriz Consolidada tiene su propio SHA en Commit (F-009 / I-010…I-017 → 3394712). Los prompts se leen en rama main: prompts/03_implementacion/.</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="14" min="1" max="1"/>
@@ -1136,17 +1136,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="J2" s="25" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="L2" s="26" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
@@ -1189,19 +1189,19 @@
           <t>src/features/auth/Login.jsx</t>
         </is>
       </c>
-      <c r="U2" s="25" t="inlineStr">
+      <c r="U2" s="26" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/features/auth/Login.jsx</t>
         </is>
       </c>
-      <c r="V2" s="25" t="inlineStr">
+      <c r="V2" s="26" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
       <c r="W2" s="22" t="inlineStr">
         <is>
-          <t>documents/04_testing/plan_pruebas_funcionales.md (casos AUTH)</t>
+          <t>backend/tests/AuthMiddlewareTest.php</t>
         </is>
       </c>
       <c r="X2" s="22" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="Z2" s="22" t="inlineStr">
         <is>
-          <t>Origen JWT: 5ce7575 [I-006]. RBAC en servidor: I-009. También AuthMiddleware.php, Jwt.php y AuthContext.jsx.</t>
+          <t>Origen JWT: 5ce7575 [I-006]. RBAC en servidor: I-009. PHPUnit de requireRole. E2E AUTH en plan_pruebas_funcionales.md.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" s="14">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>configuracion</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>Áreas y personal (RBAC organizacional)</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>Áreas, gerencias y personal (RBAC organizacional)</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Presentation (React)</t>
         </is>
@@ -1266,87 +1266,87 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J3" s="25" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K3" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" s="27" t="inlineStr">
+      <c r="L3" s="28" t="inlineStr">
         <is>
           <t>I-005</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr">
+      <c r="M3" s="27" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="O3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="26" t="inlineStr">
+      <c r="N3" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q3" s="26" t="inlineStr">
-        <is>
-          <t>CRUD de áreas y usuarios con roles Administrador / Técnico / Practicante</t>
-        </is>
-      </c>
-      <c r="R3" s="26" t="inlineStr">
+      <c r="Q3" s="27" t="inlineStr">
+        <is>
+          <t>CRUD de áreas y gerencias; usuarios con roles Administrador / Técnico / Practicante</t>
+        </is>
+      </c>
+      <c r="R3" s="27" t="inlineStr">
         <is>
           <t>src/features/configuracion/</t>
         </is>
       </c>
-      <c r="S3" s="26" t="inlineStr">
+      <c r="S3" s="27" t="inlineStr">
         <is>
           <t>ConfiguracionPage.jsx</t>
         </is>
       </c>
-      <c r="T3" s="26" t="inlineStr">
+      <c r="T3" s="27" t="inlineStr">
         <is>
           <t>src/features/configuracion/components/ConfiguracionPage.jsx</t>
         </is>
       </c>
-      <c r="U3" s="27" t="inlineStr">
+      <c r="U3" s="28" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/ConfiguracionPage.jsx</t>
         </is>
       </c>
-      <c r="V3" s="27" t="inlineStr">
+      <c r="V3" s="28" t="inlineStr">
         <is>
           <t>4e08b9e</t>
         </is>
       </c>
-      <c r="W3" s="26" t="inlineStr">
-        <is>
-          <t>documents/04_testing/plan_pruebas_funcionales.md (casos CFG)</t>
-        </is>
-      </c>
-      <c r="X3" s="26" t="inlineStr">
+      <c r="W3" s="27" t="inlineStr">
+        <is>
+          <t>backend/tests/AreaTest.php</t>
+        </is>
+      </c>
+      <c r="X3" s="27" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y3" s="26" t="inlineStr">
+      <c r="Y3" s="27" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z3" s="26" t="inlineStr">
-        <is>
-          <t>SHA vigente: 4e08b9e [I-005]. requireRole Administrador: I-009. API: AreaController.php y UsuarioController.php.</t>
+      <c r="Z3" s="27" t="inlineStr">
+        <is>
+          <t>SHA origen: 4e08b9e [I-005]. requireRole: I-009. Gerencias y PUT/DELETE áreas: I-017 (3394712). También UsuarioTest.php.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1406,7 +1406,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="26" t="inlineStr">
         <is>
           <t>I-002</t>
         </is>
@@ -1449,12 +1449,12 @@
           <t>backend/api/v2/controllers/EquipoController.php</t>
         </is>
       </c>
-      <c r="U4" s="25" t="inlineStr">
+      <c r="U4" s="26" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/EquipoController.php</t>
         </is>
       </c>
-      <c r="V4" s="25" t="inlineStr">
+      <c r="V4" s="26" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
@@ -1481,27 +1481,27 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" s="14">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>ficha</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Ficha técnica y evaluación de hardware/software</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>API (PHP)</t>
         </is>
@@ -1536,75 +1536,75 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="28" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="O5" s="26" t="n">
+      <c r="N5" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="26" t="inlineStr">
+      <c r="P5" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t>Alta/edición de ficha, evaluación y bloque predictivo en UI</t>
         </is>
       </c>
-      <c r="R5" s="26" t="inlineStr">
+      <c r="R5" s="27" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/</t>
         </is>
       </c>
-      <c r="S5" s="26" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
         <is>
           <t>FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="T5" s="26" t="inlineStr">
+      <c r="T5" s="27" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="U5" s="27" t="inlineStr">
+      <c r="U5" s="28" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="V5" s="27" t="inlineStr">
+      <c r="V5" s="28" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
-      <c r="W5" s="26" t="inlineStr">
+      <c r="W5" s="27" t="inlineStr">
         <is>
           <t>documents/04_testing/plan_pruebas_funcionales.md (casos FIC)</t>
         </is>
       </c>
-      <c r="X5" s="26" t="inlineStr">
+      <c r="X5" s="27" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y5" s="26" t="inlineStr">
+      <c r="Y5" s="27" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z5" s="26" t="inlineStr">
+      <c r="Z5" s="27" t="inlineStr">
         <is>
           <t>SHA vigente: f086a63 [I-003]. Bloque predictivo en ficha: 8b20337 [I-008].</t>
         </is>
@@ -1656,7 +1656,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1666,7 +1666,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
@@ -1709,12 +1709,12 @@
           <t>backend/api/v2/controllers/MantenimientoController.php</t>
         </is>
       </c>
-      <c r="U6" s="25" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/MantenimientoController.php</t>
         </is>
       </c>
-      <c r="V6" s="25" t="inlineStr">
+      <c r="V6" s="26" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
@@ -1741,27 +1741,27 @@
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" s="14">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Indicadores operativos y consulta de equipos por etiquetas</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Presentation (React)</t>
         </is>
@@ -1786,7 +1786,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1796,75 +1796,75 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="L7" s="28" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>CoT guiado</t>
         </is>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="O7" s="26" t="n">
+      <c r="N7" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="26" t="inlineStr">
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>Dashboard de métricas, alertas ML y panel de consulta con filtros</t>
         </is>
       </c>
-      <c r="R7" s="26" t="inlineStr">
+      <c r="R7" s="27" t="inlineStr">
         <is>
           <t>src/features/dashboard/</t>
         </is>
       </c>
-      <c r="S7" s="26" t="inlineStr">
+      <c r="S7" s="27" t="inlineStr">
         <is>
           <t>DashboardPage.jsx</t>
         </is>
       </c>
-      <c r="T7" s="26" t="inlineStr">
+      <c r="T7" s="27" t="inlineStr">
         <is>
           <t>src/features/dashboard/components/DashboardPage.jsx</t>
         </is>
       </c>
-      <c r="U7" s="27" t="inlineStr">
+      <c r="U7" s="28" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/features/dashboard/components/DashboardPage.jsx</t>
         </is>
       </c>
-      <c r="V7" s="27" t="inlineStr">
+      <c r="V7" s="28" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
-      <c r="W7" s="26" t="inlineStr">
+      <c r="W7" s="27" t="inlineStr">
         <is>
           <t>backend/tests/DashboardConsultaTest.php</t>
         </is>
       </c>
-      <c r="X7" s="26" t="inlineStr">
+      <c r="X7" s="27" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y7" s="26" t="inlineStr">
+      <c r="Y7" s="27" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z7" s="26" t="inlineStr">
+      <c r="Z7" s="27" t="inlineStr">
         <is>
           <t>Commit 5ce7575 [I-006] (dashboard de métricas + JWT). Alertas ML: I-007. Consulta tipo_otro: I-008.</t>
         </is>
@@ -1916,7 +1916,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1926,7 +1926,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>I-007</t>
         </is>
@@ -1969,12 +1969,12 @@
           <t>ml/app/main.py</t>
         </is>
       </c>
-      <c r="U8" s="25" t="inlineStr">
+      <c r="U8" s="26" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/ml/app/main.py</t>
         </is>
       </c>
-      <c r="V8" s="25" t="inlineStr">
+      <c r="V8" s="26" t="inlineStr">
         <is>
           <t>e9a0965</t>
         </is>
@@ -2001,27 +2001,27 @@
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" s="14">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>F-008</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>reportes</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Reportes PDF de ficha técnica y mantenimiento</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Reportes PDF de ficha, mantenimiento y cronograma</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>API (PHP)</t>
         </is>
@@ -2046,91 +2046,220 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J9" s="25" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="M9" s="27" t="inlineStr">
+        <is>
+          <t>Zero-shot + few-shot</t>
+        </is>
+      </c>
+      <c r="N9" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q9" s="27" t="inlineStr">
+        <is>
+          <t>PDF de ficha, historial de mantenimiento y matriz de cronograma (A4 L–V) con JWT</t>
+        </is>
+      </c>
+      <c r="R9" s="27" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S9" s="27" t="inlineStr">
+        <is>
+          <t>ReporteController.php</t>
+        </is>
+      </c>
+      <c r="T9" s="27" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="U9" s="28" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="V9" s="28" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W9" s="27" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X9" s="27" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y9" s="27" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z9" s="27" t="inlineStr">
+        <is>
+          <t>SHA origen ficha: f086a63 [I-004]. Descarga JWT: 5ce7575 [I-006]. PDF cronograma (matriz papel A4): I-012…I-016 (3394712).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="14">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Cronograma anual de preventivo (historial, matriz Xn, PDF, gerencias)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" s="27" t="inlineStr">
-        <is>
-          <t>I-004</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="inlineStr">
-        <is>
-          <t>Zero-shot + few-shot</t>
-        </is>
-      </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="O9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="26" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q9" s="26" t="inlineStr">
-        <is>
-          <t>PDF de ficha de equipo e historial/detalle de mantenimiento con JWT en descarga</t>
-        </is>
-      </c>
-      <c r="R9" s="26" t="inlineStr">
-        <is>
-          <t>backend/api/v2/controllers/</t>
-        </is>
-      </c>
-      <c r="S9" s="26" t="inlineStr">
-        <is>
-          <t>ReporteController.php</t>
-        </is>
-      </c>
-      <c r="T9" s="26" t="inlineStr">
-        <is>
-          <t>backend/api/v2/controllers/ReporteController.php</t>
-        </is>
-      </c>
-      <c r="U9" s="27" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/ReporteController.php</t>
-        </is>
-      </c>
-      <c r="V9" s="27" t="inlineStr">
-        <is>
-          <t>f086a63</t>
-        </is>
-      </c>
-      <c r="W9" s="26" t="inlineStr">
-        <is>
-          <t>documents/04_testing/plan_pruebas_funcionales.md (casos RPT)</t>
-        </is>
-      </c>
-      <c r="X9" s="26" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>Historial de planes, matriz área×día×cantidad, personal, PDF A4 y bandas de gerencia</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/</t>
+        </is>
+      </c>
+      <c r="S10" s="22" t="inlineStr">
+        <is>
+          <t>CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="T10" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="U10" s="26" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="V10" s="26" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W10" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X10" s="22" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y9" s="26" t="inlineStr">
+      <c r="Y10" s="22" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z9" s="26" t="inlineStr">
-        <is>
-          <t>SHA vigente: f086a63 [I-004]. Descarga con JWT (blob): 5ce7575 [I-006].</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29" customHeight="1" s="14"/>
+      <c r="Z10" s="22" t="inlineStr">
+        <is>
+          <t>Incremento 8 cerrado 2026-09-17 (0.10.0–0.10.7). Origen I-010; parches I-011…I-017. SHA: 3394712. También cronogramaUtils.test.js. API: CronogramaController.php.</t>
+        </is>
+      </c>
+    </row>
     <row r="11" ht="29" customHeight="1" s="14"/>
     <row r="12" ht="29" customHeight="1" s="14"/>
     <row r="13" ht="29" customHeight="1" s="14"/>
@@ -2141,7 +2270,7 @@
     <row r="18" ht="29" customHeight="1" s="14"/>
     <row r="20" ht="29" customHeight="1" s="14"/>
   </sheetData>
-  <autoFilter ref="A1:Z9"/>
+  <autoFilter ref="A1:Z10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId2"/>
@@ -2167,6 +2296,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2178,7 +2310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -2250,7 +2382,7 @@
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" s="14">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
@@ -2298,69 +2430,69 @@
           <t>Login JWT funcional (AuthContext, PrivateRoute, middleware)</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="K2" s="26" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" s="14">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>I-005</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React. Contexto: áreas y responsables no deben estar hardcodeados en EquipoForm; tablas v2_areas y v2_usuarios existen; ruta /v2/configuracion; roles Administrador, Tecnico, Practicante. Objetivo: CRUD de áreas y alta/listado de personal. Tarea: modelos PDO; password_hash BCRYPT; rutas /areas y /usuarios; ConfiguracionPage (pestañas); EquipoForm consume áreas desde API. Restricciones: no MD5; no requireRole en este incremento (deuda → I-009). Criterios: crear un área y verla en EquipoForm; usuario con hash en BD.</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="F3" s="26" t="n">
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F3" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>La API de usuarios quedó solo autenticada. I-009 añade requireRole Administrador.</t>
         </is>
       </c>
-      <c r="H3" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>Áreas y personal funcionales; EquipoForm dinámico</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t>4e08b9e</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" s="14">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>I-002</t>
         </is>
@@ -2408,69 +2540,69 @@
           <t>CRUD de equipos con código de 12 dígitos y RAM numérica</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" s="14">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>F-004</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React; replica el patrón I-002. Contexto: equipos ya se listan; hace falta consultar/editar ficha técnica del equipo. Tarea: modelo/controlador/ruta de fichas; GET por id y por código patrimonial; acceso desde inventario (modal o /v2/ficha-tecnica). Restricciones: no PDF (I-004); no bloque ML (I-008). Criterios: GET ficha existente o vacío controlado (no 500).</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="n">
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>N/A — evaluación predictiva en ficha es I-008.</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>API y UI de ficha técnica por id o código</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="28" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" s="14">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
@@ -2518,69 +2650,69 @@
           <t>Timeline y alta estructurada de mantenimientos</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" s="14">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React (mismo incremento 0.6.0 que F-001). Objetivo: métricas operativas en GET /api/v2/dashboard y UI DashboardPage (conteos, no ML). Tarea: DashboardController + DashboardPage; no badges de riesgo (I-007); no panel de consulta por etiquetas (I-008). Restricciones: no llamar a :8000. Criterios: dashboard muestra conteos persistidos tras login.</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>CoT guiado</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="n">
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>N/A — consulta tipo_otro es I-008; alertas ML son I-007.</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>Dashboard de métricas operativas funcional</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" s="14">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>I-007</t>
         </is>
@@ -2628,69 +2760,69 @@
           <t>FastAPI + proxy PHP + badges; degradación controlada</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>e9a0965</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" s="14">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>I-004</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>F-008</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP (dompdf) y React. Contexto: inventario y ficha ya existen. Objetivo: GET /api/v2/reportes/equipo/{id} genera PDF; InventarioPage filtra en cliente y ofrece descargar ficha. Tarea: Composer dompdf; ReporteController HTML→PDF; botón en la fila. Restricciones: PDF binario, no base64; no reportes de mantenimiento en este incremento. Criterios: PDF muestra código patrimonial; filtro de texto reduce filas.</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Zero-shot + few-shot</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="n">
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>window.open sin token; I-006 cambia la descarga a blob + Authorization.</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="27" t="inlineStr">
         <is>
           <t>PDF de ficha y filtros de inventario funcionales</t>
         </is>
       </c>
-      <c r="K9" s="27" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" s="14">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>I-008</t>
         </is>
@@ -2738,64 +2870,504 @@
           <t>Telemetría, sync, ficha predictiva y consulta de equipos</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" s="14">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>I-009</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>F-001, F-002, F-003</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior de API PHP y React. Contexto: 0.9.1; JWT existe; un Técnico puede mutar /usuarios; plantilla Excel desalinea numero_serie/area por falta de color. Objetivo: requireRole Administrador en escritura de usuarios; no autoeliminación ni borrar el último admin; RoleRoute en Configuración; fila ejemplo Excel alineada. Criterios: Técnico en POST /usuarios → 403.</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>CoT guiado</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="n">
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>I-005 no puso autorización en servidor (deuda de RBAC).</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>requireRole en /usuarios y plantilla Excel alineada</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>8b20337</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1" s="14">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: 0.9.1; R-006 y D-007; ADR-003 (v2_cronogramas / v2_cronograma_celdas); no usar v2_cronograma_mantenimiento. Objetivo: historial, alta de documento, matriz área×día×turno, cobertura y PDF. Tarea: SQL+migrate; modelo; controller; GET /reportes/cronograma/{id}; feature cronograma; Navbar; PHPUnit/Vitest. Restricciones: no ML; no dual-write; Practicante GET sí / POST 403. Criterios: dos planes el mismo año; clic crea/libera celda; PDF autenticado.</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>N/A en origen. Totales, PDF papel, Xn, A4, gerencias = I-011…I-017.</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Historial, matriz y PDF autenticado (0.10.0)</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1" s="14">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>I-011</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: 0.10.0. Faltan subtotal/total; hay que programar hora de cada equipo; Imprimir PDF abre pestaña en blanco. Objetivo: parche 0.10.1. El asiento sigue área+fecha+turno (ADR-003). Tarea: columna Tot y pie Subtotal/Total; v2_cronograma_horarios + modal PUT; downloadPdf con attachment y Content-Type PDF. Criterios: pie de totales; modal horas; PDF descarga archivo.</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>I-010 no tenía totales ni horas por equipo; downloadPdf sin attachment.</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J13" s="27" t="inlineStr">
+        <is>
+          <t>Totales, horarios por equipo e impresión con download</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1" s="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>I-012</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>F-008, F-009</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / Dompdf. Contexto: el PDF era un listado; el papel 2024 es una matriz N°/área/PC/laptop/impresora × meses y días con marcas X1/X2. Objetivo: GET /reportes/cronograma/{id} imprime esa grilla. Tarea: A3 apaisado; rango de meses con marca; un día = una columna; última hoja leyenda y nota. No cambiar el asiento. Criterios: el PDF se parece al papel; las X coinciden con la UI.</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>I-011 imprimía listado, no la grilla del papel.</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>PDF tipo matriz (papel 2024)</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1" s="14">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>I-013</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: el recuadro HORA PROGRAMADA del papel son las personas que hacen el preventivo, no los bienes del área. Objetivo: recuadro editable en matriz y PDF. Tarea: v2_cronograma_personal; PUT /cronogramas/{id}/personal; quitar del PDF la tabla grande de horas por CPU. Criterios: se edita el nombre y se ve igual en el PDF.</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>I-012 listaba PCs del inventario en HORA PROGRAMADA; el papel lista personas.</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>Personal del preventivo en HORA PROGRAMADA</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1" s="14">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>I-014</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: X1/X2 no son mañana/tarde: son cuántos PC/laptop se atienden ese día. Objetivo: asiento = cronograma + área + fecha + cantidad; una columna por día. Tarea: SQL cantidad + UNIQUE(área,fecha); POST {cantidad}; selector X1…Xn; cobertura = suma(cantidad) vs PC+laptop. Restricciones: no 10 columnas; no auto-fill; impresoras no entran en Xn.</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>I-010 modeló X1/X2 como turnos; el papel usa cantidad por día.</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Xn = cantidad por día (no turnos)</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1" s="14">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>I-015</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19 / Dompdf. Contexto: PDF A3 4 meses con sábados/domingos; hace falta A4, L–V, 2 meses/hoja, año del documento y poder borrar un plan. Objetivo: PDF A4 apaisado laborable; DELETE /cronogramas/{id} CASCADE; matriz UI sin fines de semana. Restricciones: no auto-fill; Practicante no elimina; conservar N°/área/conteos.</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>I-012 era A3 calendario completo; el responsable pidió A4 laborable y baja.</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="inlineStr">
+        <is>
+          <t>PDF A4 L–V 2 meses/hoja y DELETE del plan</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1" s="14">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>I-016</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>F-008, F-009</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / Dompdf. Contexto: el PDF A4 aplastaba ÁREA (colspan calendario vs L–V); N° enorme; PC/LAP/IMP acrónimos; dos tablas desalineadas; HORA PROGRAMADA sin reja. Objetivo: una sola tabla; textos sin distorsión; pie N°/EQUIPO/HORARIO con borde. Criterios: áreas se leen; PC/LAPTOP/IMPRESORA completos; filas Xn alineadas.</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>I-015 encajaba mal colspan y el pie no tenía borde.</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>PDF encajado; HORA PROGRAMADA con borde</t>
+        </is>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1" s="14">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>I-017</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>F-002, F-009</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: el papel agrupa áreas bajo filas de gerencia; v2_areas solo tenía alta. Objetivo: catálogo v2_gerencias; área.gerencia_id; CRUD de área (Admin); matriz y PDF con fila banda. Restricciones: no auto-fill; SIGA/SAF son áreas, no gerencias; no borrar área con equipos (409); no etiqueta libre. Criterios: asignar gerencia; 409 si hay equipos; bandas en cronograma/PDF.</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>Cierre del Incremento 8: gerencias del papel y CRUD de áreas pendiente desde I-005.</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Gerencias, CRUD de áreas y bandas en cronograma (0.10.7)</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="inlineStr">
+        <is>
+          <t>3394712</t>
         </is>
       </c>
     </row>
@@ -2821,6 +3393,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3052,7 +3640,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Identificador del prompt vigente (I-002…I-009). Una fila por función F-001…F-008 en Prompts Detallados. Hipervínculo al markdown en GitHub (prompts/).</t>
+          <t>Identificador del prompt vigente (I-002…I-017). Una fila por función F-001…F-009 en Prompts Detallados, más refinamientos. Hipervínculo al markdown en GitHub (prompts/).</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">

--- a/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
+++ b/documents/matriz_doble_entrada/MATRIZ-DOBLE-ENTRADA-V3-SIGEMAD-MPA.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario de Columnas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Matriz Consolidada'!$A$1:$Z$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Matriz Consolidada'!$A$1:$Z$52</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -130,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -251,16 +251,16 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -685,7 +685,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad los IDs vigentes son I-002…I-017 (una fila por función F-001…F-009 en Prompts Detallados, más refinamientos I-008…I-017).</t>
+          <t>Aporta el modelo de versionado y gestión de calidad de prompts (control de iteraciones, criterio de aceptación). Se refleja en 'ID Prompt', 'Versión del prompt', 'N.º de iteraciones' y 'Criterio de aceptación'. En Sigemad cada fila de Matriz Consolidada es una función atómica (F-001 inicio de sesión, F-011 registro de usuario, …), no un módulo entero. Los IDs de prompt vigentes son I-002…I-017.</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Busca en 'Matriz Consolidada' por 'Feature/Módulo' (auth, inventario, ficha, mantenimiento, dashboard, ml, reportes, configuracion, cronograma) o 'ID Función' (F-001 a F-009).</t>
+          <t>Busca en 'Matriz Consolidada' por 'Feature/Módulo' (auth, configuracion, inventario, ficha, mantenimiento, dashboard, ml, reportes, cronograma) o 'ID Función' (F-001 a F-051). Una fila = una función (login distinto de registro, alta de área distinta de baja).</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="10" customWidth="1" style="14" min="1" max="1"/>
-    <col width="14" customWidth="1" style="14" min="2" max="2"/>
-    <col width="26" customWidth="1" style="14" min="3" max="3"/>
+    <col width="12" customWidth="1" style="14" min="1" max="1"/>
+    <col width="16" customWidth="1" style="14" min="2" max="2"/>
+    <col width="38" customWidth="1" style="14" min="3" max="3"/>
     <col width="14" customWidth="1" style="14" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="22" customWidth="1" style="14" min="6" max="6"/>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" s="14">
+    <row r="2" ht="36" customHeight="1" s="14">
       <c r="A2" s="22" t="inlineStr">
         <is>
           <t>F-001</t>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>Autenticación JWT y sesión (login, RBAC)</t>
+          <t>Inicio de sesión</t>
         </is>
       </c>
       <c r="D2" s="22" t="inlineStr">
@@ -1136,9 +1136,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="J2" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" s="23" t="inlineStr">
@@ -1146,7 +1146,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="26" t="inlineStr">
+      <c r="L2" s="25" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="Q2" s="22" t="inlineStr">
         <is>
-          <t>Login JWT, AuthContext, middleware y protección de rutas API/UI</t>
+          <t>POST /auth/login emite JWT y redirige a /v2/dashboard</t>
         </is>
       </c>
       <c r="R2" s="22" t="inlineStr">
@@ -1189,19 +1189,19 @@
           <t>src/features/auth/Login.jsx</t>
         </is>
       </c>
-      <c r="U2" s="26" t="inlineStr">
+      <c r="U2" s="25" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/features/auth/Login.jsx</t>
         </is>
       </c>
-      <c r="V2" s="26" t="inlineStr">
+      <c r="V2" s="25" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
       <c r="W2" s="22" t="inlineStr">
         <is>
-          <t>backend/tests/AuthMiddlewareTest.php</t>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (AUTH-001)</t>
         </is>
       </c>
       <c r="X2" s="22" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="Z2" s="22" t="inlineStr">
         <is>
-          <t>Origen JWT: 5ce7575 [I-006]. RBAC en servidor: I-009. PHPUnit de requireRole. E2E AUTH en plan_pruebas_funcionales.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1" s="14">
-      <c r="A3" s="27" t="inlineStr">
+          <t>HU-AUTH-001. Credenciales inválidas no revelan si el usuario existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="14">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>F-002</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>configuracion</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>Áreas, gerencias y personal (RBAC organizacional)</t>
-        </is>
-      </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Cerrar sesión</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>Presentation (React)</t>
         </is>
@@ -1266,9 +1266,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" s="23" t="inlineStr">
@@ -1276,81 +1276,81 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L3" s="28" t="inlineStr">
-        <is>
-          <t>I-005</t>
-        </is>
-      </c>
-      <c r="M3" s="27" t="inlineStr">
-        <is>
-          <t>Few-shot</t>
-        </is>
-      </c>
-      <c r="N3" s="27" t="inlineStr">
+      <c r="L3" s="27" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="M3" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N3" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O3" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" s="27" t="inlineStr">
+      <c r="O3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q3" s="27" t="inlineStr">
-        <is>
-          <t>CRUD de áreas y gerencias; usuarios con roles Administrador / Técnico / Practicante</t>
-        </is>
-      </c>
-      <c r="R3" s="27" t="inlineStr">
-        <is>
-          <t>src/features/configuracion/</t>
-        </is>
-      </c>
-      <c r="S3" s="27" t="inlineStr">
-        <is>
-          <t>ConfiguracionPage.jsx</t>
-        </is>
-      </c>
-      <c r="T3" s="27" t="inlineStr">
-        <is>
-          <t>src/features/configuracion/components/ConfiguracionPage.jsx</t>
-        </is>
-      </c>
-      <c r="U3" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/ConfiguracionPage.jsx</t>
-        </is>
-      </c>
-      <c r="V3" s="28" t="inlineStr">
-        <is>
-          <t>4e08b9e</t>
-        </is>
-      </c>
-      <c r="W3" s="27" t="inlineStr">
-        <is>
-          <t>backend/tests/AreaTest.php</t>
-        </is>
-      </c>
-      <c r="X3" s="27" t="inlineStr">
+      <c r="Q3" s="26" t="inlineStr">
+        <is>
+          <t>Navbar Salir limpia token y vuelve a /login</t>
+        </is>
+      </c>
+      <c r="R3" s="26" t="inlineStr">
+        <is>
+          <t>src/components/</t>
+        </is>
+      </c>
+      <c r="S3" s="26" t="inlineStr">
+        <is>
+          <t>Navbar.jsx</t>
+        </is>
+      </c>
+      <c r="T3" s="26" t="inlineStr">
+        <is>
+          <t>src/components/Navbar.jsx</t>
+        </is>
+      </c>
+      <c r="U3" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/components/Navbar.jsx</t>
+        </is>
+      </c>
+      <c r="V3" s="27" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (AUTH-004)</t>
+        </is>
+      </c>
+      <c r="X3" s="26" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y3" s="27" t="inlineStr">
+      <c r="Y3" s="26" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z3" s="27" t="inlineStr">
-        <is>
-          <t>SHA origen: 4e08b9e [I-005]. requireRole: I-009. Gerencias y PUT/DELETE áreas: I-017 (3394712). También UsuarioTest.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1" s="14">
+      <c r="Z3" s="26" t="inlineStr">
+        <is>
+          <t>HU-AUTH-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="14">
       <c r="A4" s="22" t="inlineStr">
         <is>
           <t>F-003</t>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>inventario</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>Inventario patrimonial de equipos (CRUD, filtros, carga Excel)</t>
+          <t>Persistencia de sesión</t>
         </is>
       </c>
       <c r="D4" s="22" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="E4" s="22" t="inlineStr">
         <is>
-          <t>API (PHP)</t>
+          <t>Presentation (React)</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
@@ -1396,9 +1396,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr">
@@ -1406,14 +1406,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L4" s="26" t="inlineStr">
-        <is>
-          <t>I-002</t>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>I-006</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>Few-shot</t>
+          <t>CoT guiado</t>
         </is>
       </c>
       <c r="N4" s="22" t="inlineStr">
@@ -1431,846 +1431,6297 @@
       </c>
       <c r="Q4" s="22" t="inlineStr">
         <is>
-          <t>CRUD equipos, código de 12 dígitos, tipos personalizados y carga masiva</t>
+          <t>F5 mantiene sesión vía AuthContext y localStorage</t>
         </is>
       </c>
       <c r="R4" s="22" t="inlineStr">
         <is>
+          <t>src/context/</t>
+        </is>
+      </c>
+      <c r="S4" s="22" t="inlineStr">
+        <is>
+          <t>AuthContext.jsx</t>
+        </is>
+      </c>
+      <c r="T4" s="22" t="inlineStr">
+        <is>
+          <t>src/context/AuthContext.jsx</t>
+        </is>
+      </c>
+      <c r="U4" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/context/AuthContext.jsx</t>
+        </is>
+      </c>
+      <c r="V4" s="25" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+      <c r="W4" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (AUTH-003)</t>
+        </is>
+      </c>
+      <c r="X4" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y4" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z4" s="22" t="inlineStr">
+        <is>
+          <t>HU-AUTH-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="14">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Protección JWT de la API</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="27" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N5" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
+        <is>
+          <t>Rutas V2 sin Bearer responden 401 (salvo /auth)</t>
+        </is>
+      </c>
+      <c r="R5" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/middleware/</t>
+        </is>
+      </c>
+      <c r="S5" s="26" t="inlineStr">
+        <is>
+          <t>AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="T5" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/middleware/AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="U5" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/backend/api/v2/middleware/AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="V5" s="27" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (REG-004)</t>
+        </is>
+      </c>
+      <c r="X5" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y5" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z5" s="26" t="inlineStr">
+        <is>
+          <t>HU-AUTH-002. requireAuth en index.php.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="14">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Autorización por rol (RBAC)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t>I-009</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>Técnico en POST/PUT/DELETE /usuarios → 403</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/middleware/</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t>AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="T6" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/middleware/AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="U6" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/middleware/AuthMiddleware.php</t>
+        </is>
+      </c>
+      <c r="V6" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W6" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/AuthMiddlewareTest.php</t>
+        </is>
+      </c>
+      <c r="X6" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y6" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z6" s="22" t="inlineStr">
+        <is>
+          <t>HU-AUTH-005 / HU-CFG-006. RoleRoute en UI. iter I-009.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="14">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Listado de áreas</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="27" t="inlineStr">
+        <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N7" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q7" s="26" t="inlineStr">
+        <is>
+          <t>GET /areas alimenta Configuración e Inventario</t>
+        </is>
+      </c>
+      <c r="R7" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/</t>
+        </is>
+      </c>
+      <c r="S7" s="26" t="inlineStr">
+        <is>
+          <t>ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="T7" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="U7" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="V7" s="27" t="inlineStr">
+        <is>
+          <t>4e08b9e</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CFG-001)</t>
+        </is>
+      </c>
+      <c r="X7" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y7" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z7" s="26" t="inlineStr">
+        <is>
+          <t>HU-CFG-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="14">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>F-007</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Alta de área</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="M8" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N8" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>POST /areas crea el área y aparece en EquipoForm</t>
+        </is>
+      </c>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/</t>
+        </is>
+      </c>
+      <c r="S8" s="22" t="inlineStr">
+        <is>
+          <t>AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="T8" s="22" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="U8" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="V8" s="25" t="inlineStr">
+        <is>
+          <t>4e08b9e</t>
+        </is>
+      </c>
+      <c r="W8" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CFG-002)</t>
+        </is>
+      </c>
+      <c r="X8" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y8" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z8" s="22" t="inlineStr">
+        <is>
+          <t>HU-CFG-002 / HU-CFG-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="14">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Edición de área</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>I-017</t>
+        </is>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N9" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q9" s="26" t="inlineStr">
+        <is>
+          <t>PUT /areas?id= actualiza nombre, jefe y gerencia</t>
+        </is>
+      </c>
+      <c r="R9" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/</t>
+        </is>
+      </c>
+      <c r="S9" s="26" t="inlineStr">
+        <is>
+          <t>AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="T9" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="U9" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/configuracion/components/AreaForm.jsx</t>
+        </is>
+      </c>
+      <c r="V9" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CFG-009)</t>
+        </is>
+      </c>
+      <c r="X9" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y9" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z9" s="26" t="inlineStr">
+        <is>
+          <t>HU-CFG-007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="14">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Baja de área</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>I-017</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>DELETE /areas?id= 204; 409 si el área tiene equipos</t>
+        </is>
+      </c>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/</t>
+        </is>
+      </c>
+      <c r="S10" s="22" t="inlineStr">
+        <is>
+          <t>Area.php</t>
+        </is>
+      </c>
+      <c r="T10" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/Area.php</t>
+        </is>
+      </c>
+      <c r="U10" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/models/Area.php</t>
+        </is>
+      </c>
+      <c r="V10" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W10" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/AreaTest.php</t>
+        </is>
+      </c>
+      <c r="X10" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y10" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z10" s="22" t="inlineStr">
+        <is>
+          <t>HU-CFG-007. Solo Administrador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="14">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Listado de personal</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N11" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t>GET /usuarios lista personal con rol y área</t>
+        </is>
+      </c>
+      <c r="R11" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/</t>
+        </is>
+      </c>
+      <c r="S11" s="26" t="inlineStr">
+        <is>
+          <t>ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="T11" s="26" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="U11" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/ConfiguracionPage.jsx</t>
+        </is>
+      </c>
+      <c r="V11" s="27" t="inlineStr">
+        <is>
+          <t>4e08b9e</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CFG-003)</t>
+        </is>
+      </c>
+      <c r="X11" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y11" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z11" s="26" t="inlineStr">
+        <is>
+          <t>HU-CFG-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="14">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Registro de usuario</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>I-005</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N12" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>POST /usuarios crea cuenta con password BCRYPT (solo Admin)</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t>UsuarioForm.jsx</t>
+        </is>
+      </c>
+      <c r="T12" s="22" t="inlineStr">
+        <is>
+          <t>src/features/configuracion/components/UsuarioForm.jsx</t>
+        </is>
+      </c>
+      <c r="U12" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/4e08b9e/src/features/configuracion/components/UsuarioForm.jsx</t>
+        </is>
+      </c>
+      <c r="V12" s="25" t="inlineStr">
+        <is>
+          <t>4e08b9e</t>
+        </is>
+      </c>
+      <c r="W12" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/UsuarioTest.php</t>
+        </is>
+      </c>
+      <c r="X12" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y12" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z12" s="22" t="inlineStr">
+        <is>
+          <t>HU-CFG-004. No hay auto-registro público.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="14">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>F-012</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Edición y baja de usuario</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>I-009</t>
+        </is>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N13" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q13" s="26" t="inlineStr">
+        <is>
+          <t>PUT/DELETE /usuarios; no autoeliminación ni borrar el último admin</t>
+        </is>
+      </c>
+      <c r="R13" s="26" t="inlineStr">
+        <is>
           <t>backend/api/v2/controllers/</t>
         </is>
       </c>
-      <c r="S4" s="22" t="inlineStr">
+      <c r="S13" s="26" t="inlineStr">
+        <is>
+          <t>UsuarioController.php</t>
+        </is>
+      </c>
+      <c r="T13" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/UsuarioController.php</t>
+        </is>
+      </c>
+      <c r="U13" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/controllers/UsuarioController.php</t>
+        </is>
+      </c>
+      <c r="V13" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="inlineStr">
+        <is>
+          <t>backend/tests/UsuarioTest.php</t>
+        </is>
+      </c>
+      <c r="X13" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y13" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z13" s="26" t="inlineStr">
+        <is>
+          <t>HU-CFG-006. requireRole Administrador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>F-013</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>configuracion</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Catálogo de gerencias</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>I-017</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>CRUD /gerencias; área.gerencia_id opcional (selector, no etiqueta libre)</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>GerenciaController.php</t>
+        </is>
+      </c>
+      <c r="T14" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/GerenciaController.php</t>
+        </is>
+      </c>
+      <c r="U14" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/controllers/GerenciaController.php</t>
+        </is>
+      </c>
+      <c r="V14" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W14" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CFG-010)</t>
+        </is>
+      </c>
+      <c r="X14" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y14" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z14" s="22" t="inlineStr">
+        <is>
+          <t>HU-CFG-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="14">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>F-014</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Listado de equipos</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>I-002</t>
+        </is>
+      </c>
+      <c r="M15" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N15" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q15" s="26" t="inlineStr">
+        <is>
+          <t>GET /equipos muestra tabla patrimonial</t>
+        </is>
+      </c>
+      <c r="R15" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S15" s="26" t="inlineStr">
+        <is>
+          <t>InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="T15" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="U15" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="V15" s="27" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (INV-001)</t>
+        </is>
+      </c>
+      <c r="X15" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y15" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z15" s="26" t="inlineStr">
+        <is>
+          <t>HU-INV-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="14">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>F-015</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Alta de equipo</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>I-002</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>POST /equipos persiste código patrimonial de 12 dígitos</t>
+        </is>
+      </c>
+      <c r="R16" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>EquipoForm.jsx</t>
+        </is>
+      </c>
+      <c r="T16" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/EquipoForm.jsx</t>
+        </is>
+      </c>
+      <c r="U16" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/src/features/inventario/components/EquipoForm.jsx</t>
+        </is>
+      </c>
+      <c r="V16" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W16" s="22" t="inlineStr">
+        <is>
+          <t>src/lib/equipoTipo.test.js</t>
+        </is>
+      </c>
+      <c r="X16" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y16" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z16" s="22" t="inlineStr">
+        <is>
+          <t>HU-INV-002 / HU-INV-008. RAM numérica, no texto “8 GB”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="14">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Edición de equipo</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="27" t="inlineStr">
+        <is>
+          <t>I-002</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N17" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q17" s="26" t="inlineStr">
+        <is>
+          <t>GET/PUT /equipos/{id} actualiza ficha de inventario</t>
+        </is>
+      </c>
+      <c r="R17" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S17" s="26" t="inlineStr">
         <is>
           <t>EquipoController.php</t>
         </is>
       </c>
-      <c r="T4" s="22" t="inlineStr">
+      <c r="T17" s="26" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/EquipoController.php</t>
         </is>
       </c>
-      <c r="U4" s="26" t="inlineStr">
+      <c r="U17" s="27" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/EquipoController.php</t>
         </is>
       </c>
-      <c r="V4" s="26" t="inlineStr">
+      <c r="V17" s="27" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
-      <c r="W4" s="22" t="inlineStr">
-        <is>
-          <t>src/lib/equipoTipo.test.js</t>
-        </is>
-      </c>
-      <c r="X4" s="22" t="inlineStr">
+      <c r="W17" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (INV-010)</t>
+        </is>
+      </c>
+      <c r="X17" s="26" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y4" s="22" t="inlineStr">
+      <c r="Y17" s="26" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z4" s="22" t="inlineStr">
-        <is>
-          <t>SHA vigente: f086a63 [I-002]. Telemetría: I-008. Plantilla Excel: I-009. Test unitario de tipo de equipo (Vitest).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1" s="14">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>F-004</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="Z17" s="26" t="inlineStr">
+        <is>
+          <t>HU-INV-009.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="14">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>F-017</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Filtro de inventario</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" s="25" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>Filtro de texto reduce filas en cliente</t>
+        </is>
+      </c>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="T18" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="U18" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="V18" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W18" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (INV-003)</t>
+        </is>
+      </c>
+      <c r="X18" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y18" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z18" s="22" t="inlineStr">
+        <is>
+          <t>HU-INV-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="14">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>F-018</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Plantilla Excel de carga</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="27" t="inlineStr">
+        <is>
+          <t>I-009</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N19" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q19" s="26" t="inlineStr">
+        <is>
+          <t>GET /equipos/plantilla descarga .xlsx con columna color alineada</t>
+        </is>
+      </c>
+      <c r="R19" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S19" s="26" t="inlineStr">
+        <is>
+          <t>EquipoController.php</t>
+        </is>
+      </c>
+      <c r="T19" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/EquipoController.php</t>
+        </is>
+      </c>
+      <c r="U19" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/controllers/EquipoController.php</t>
+        </is>
+      </c>
+      <c r="V19" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="inlineStr">
+        <is>
+          <t>backend/tests/EquipoPlantillaTest.php</t>
+        </is>
+      </c>
+      <c r="X19" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y19" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z19" s="26" t="inlineStr">
+        <is>
+          <t>HU-INV-004. Fila de ejemplo no desplaza numero_serie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="14">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Carga masiva Excel</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>I-002</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>POST /equipos/carga-masiva importa filas .xlsx</t>
+        </is>
+      </c>
+      <c r="R20" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S20" s="22" t="inlineStr">
+        <is>
+          <t>EquipoController.php</t>
+        </is>
+      </c>
+      <c r="T20" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/EquipoController.php</t>
+        </is>
+      </c>
+      <c r="U20" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/EquipoController.php</t>
+        </is>
+      </c>
+      <c r="V20" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W20" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (INV-005)</t>
+        </is>
+      </c>
+      <c r="X20" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y20" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z20" s="22" t="inlineStr">
+        <is>
+          <t>HU-INV-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="14">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>F-020</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>inventario</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Indicador de riesgo en inventario</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" s="27" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M21" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N21" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q21" s="26" t="inlineStr">
+        <is>
+          <t>Columna Riesgo ML (badge) vía predicción por lote</t>
+        </is>
+      </c>
+      <c r="R21" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S21" s="26" t="inlineStr">
+        <is>
+          <t>InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="T21" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="U21" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/src/features/inventario/components/InventarioPage.jsx</t>
+        </is>
+      </c>
+      <c r="V21" s="27" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (ML-002)</t>
+        </is>
+      </c>
+      <c r="X21" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y21" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z21" s="26" t="inlineStr">
+        <is>
+          <t>HU-INV-006 / HU-ML-002.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="14">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>F-021</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>ficha</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Ficha técnica y evaluación de hardware/software</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Búsqueda de ficha por código</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>GET /fichas-tecnicas/buscar/{codigo} (12 dígitos)</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S22" s="22" t="inlineStr">
+        <is>
+          <t>FichaTecnicaPage.jsx</t>
+        </is>
+      </c>
+      <c r="T22" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/FichaTecnicaPage.jsx</t>
+        </is>
+      </c>
+      <c r="U22" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/src/features/inventario/components/FichaTecnicaPage.jsx</t>
+        </is>
+      </c>
+      <c r="V22" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W22" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (FIC-001)</t>
+        </is>
+      </c>
+      <c r="X22" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y22" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z22" s="22" t="inlineStr">
+        <is>
+          <t>HU-FIC-001. Vacío controlado, no 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="14">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>F-022</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>ficha</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Consulta de ficha técnica</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>API (PHP)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Alto (integración/validación)</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L5" s="28" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" s="27" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M23" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="N23" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O5" s="27" t="n">
+      <c r="O23" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="27" t="inlineStr">
+      <c r="P23" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
-        <is>
-          <t>Alta/edición de ficha, evaluación y bloque predictivo en UI</t>
-        </is>
-      </c>
-      <c r="R5" s="27" t="inlineStr">
+      <c r="Q23" s="26" t="inlineStr">
+        <is>
+          <t>GET /fichas-tecnicas/{id} devuelve hardware/software</t>
+        </is>
+      </c>
+      <c r="R23" s="26" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/</t>
         </is>
       </c>
-      <c r="S5" s="27" t="inlineStr">
+      <c r="S23" s="26" t="inlineStr">
         <is>
           <t>FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="T5" s="27" t="inlineStr">
+      <c r="T23" s="26" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="U5" s="28" t="inlineStr">
+      <c r="U23" s="27" t="inlineStr">
         <is>
           <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/FichaTecnicaController.php</t>
         </is>
       </c>
-      <c r="V5" s="28" t="inlineStr">
+      <c r="V23" s="27" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
-      <c r="W5" s="27" t="inlineStr">
-        <is>
-          <t>documents/04_testing/plan_pruebas_funcionales.md (casos FIC)</t>
-        </is>
-      </c>
-      <c r="X5" s="27" t="inlineStr">
+      <c r="W23" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (FIC-002)</t>
+        </is>
+      </c>
+      <c r="X23" s="26" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y5" s="27" t="inlineStr">
+      <c r="Y23" s="26" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z5" s="27" t="inlineStr">
-        <is>
-          <t>SHA vigente: f086a63 [I-003]. Bloque predictivo en ficha: 8b20337 [I-008].</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" s="14">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>F-005</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="Z23" s="26" t="inlineStr">
+        <is>
+          <t>HU-FIC-002 / HU-INV-007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="14">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>F-023</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>ficha</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Edición de evaluación técnica</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>PUT ficha persiste conservación, estado y observaciones</t>
+        </is>
+      </c>
+      <c r="R24" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S24" s="22" t="inlineStr">
+        <is>
+          <t>FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="T24" s="22" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="U24" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/src/features/inventario/components/FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="V24" s="25" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W24" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (FIC-003)</t>
+        </is>
+      </c>
+      <c r="X24" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y24" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z24" s="22" t="inlineStr">
+        <is>
+          <t>HU-FIC-003–007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="14">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>F-024</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>ficha</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Bloque predictivo en ficha</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>I-008</t>
+        </is>
+      </c>
+      <c r="M25" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N25" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q25" s="26" t="inlineStr">
+        <is>
+          <t>La ficha muestra score de riesgo si FastAPI está arriba</t>
+        </is>
+      </c>
+      <c r="R25" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/</t>
+        </is>
+      </c>
+      <c r="S25" s="26" t="inlineStr">
+        <is>
+          <t>FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="T25" s="26" t="inlineStr">
+        <is>
+          <t>src/features/inventario/components/FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="U25" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/src/features/inventario/components/FichaTecnicaPanel.jsx</t>
+        </is>
+      </c>
+      <c r="V25" s="27" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (FIC-008)</t>
+        </is>
+      </c>
+      <c r="X25" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y25" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z25" s="26" t="inlineStr">
+        <is>
+          <t>HU-FIC-008. iter I-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="14">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>F-025</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>mantenimiento</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>Historial de mantenimiento, telemetría y correctivo estructurado</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Timeline de mantenimientos</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
+        <is>
+          <t>GET /mantenimientos lista intervenciones con categoría nombrada</t>
+        </is>
+      </c>
+      <c r="R26" s="22" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/</t>
+        </is>
+      </c>
+      <c r="S26" s="22" t="inlineStr">
+        <is>
+          <t>MantenimientoPage.jsx</t>
+        </is>
+      </c>
+      <c r="T26" s="22" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/MantenimientoPage.jsx</t>
+        </is>
+      </c>
+      <c r="U26" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/src/features/mantenimiento/components/MantenimientoPage.jsx</t>
+        </is>
+      </c>
+      <c r="V26" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W26" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (MNT-001)</t>
+        </is>
+      </c>
+      <c r="X26" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y26" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z26" s="22" t="inlineStr">
+        <is>
+          <t>HU-MNT-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" s="14">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>F-026</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Registro de intervención</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" s="27" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N27" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q27" s="26" t="inlineStr">
+        <is>
+          <t>POST /mantenimientos liga equipo_id; categoría obligatoria en correctivo</t>
+        </is>
+      </c>
+      <c r="R27" s="26" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/</t>
+        </is>
+      </c>
+      <c r="S27" s="26" t="inlineStr">
+        <is>
+          <t>MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="T27" s="26" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="U27" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/src/features/mantenimiento/components/MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="V27" s="27" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (MNT-002)</t>
+        </is>
+      </c>
+      <c r="X27" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y27" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z27" s="26" t="inlineStr">
+        <is>
+          <t>HU-MNT-002 / HU-MNT-007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="14">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>F-027</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Detalle de intervención</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
+        <is>
+          <t>GET /mantenimientos/{id} abre modal de ficha de intervención</t>
+        </is>
+      </c>
+      <c r="R28" s="22" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/</t>
+        </is>
+      </c>
+      <c r="S28" s="22" t="inlineStr">
+        <is>
+          <t>MantenimientoDetalleModal.jsx</t>
+        </is>
+      </c>
+      <c r="T28" s="22" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/MantenimientoDetalleModal.jsx</t>
+        </is>
+      </c>
+      <c r="U28" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/src/features/mantenimiento/components/MantenimientoDetalleModal.jsx</t>
+        </is>
+      </c>
+      <c r="V28" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W28" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (MNT-004)</t>
+        </is>
+      </c>
+      <c r="X28" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y28" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z28" s="22" t="inlineStr">
+        <is>
+          <t>HU-MNT-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="14">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>F-028</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Historial por código patrimonial</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>API (PHP)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N29" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q29" s="26" t="inlineStr">
+        <is>
+          <t>GET /mantenimientos/historial/{codigo} filtra timeline de un equipo</t>
+        </is>
+      </c>
+      <c r="R29" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S29" s="26" t="inlineStr">
+        <is>
+          <t>MantenimientoController.php</t>
+        </is>
+      </c>
+      <c r="T29" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/MantenimientoController.php</t>
+        </is>
+      </c>
+      <c r="U29" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/MantenimientoController.php</t>
+        </is>
+      </c>
+      <c r="V29" s="27" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (MNT-003)</t>
+        </is>
+      </c>
+      <c r="X29" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y29" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z29" s="26" t="inlineStr">
+        <is>
+          <t>HU-MNT-003 / HU-MNT-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="14">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>F-029</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Sincronización de telemetría</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Alto (integración/validación)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" s="28" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="26" t="inlineStr">
-        <is>
-          <t>I-003</t>
-        </is>
-      </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>I-008</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>Al registrar mantenimiento se actualiza snapshot del equipo</t>
+        </is>
+      </c>
+      <c r="R30" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/</t>
+        </is>
+      </c>
+      <c r="S30" s="22" t="inlineStr">
+        <is>
+          <t>Mantenimiento.php</t>
+        </is>
+      </c>
+      <c r="T30" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/Mantenimiento.php</t>
+        </is>
+      </c>
+      <c r="U30" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/models/Mantenimiento.php</t>
+        </is>
+      </c>
+      <c r="V30" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W30" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/MantenimientoTest.php</t>
+        </is>
+      </c>
+      <c r="X30" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y30" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z30" s="22" t="inlineStr">
+        <is>
+          <t>HU-MNT-010. iter I-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="14">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>F-030</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Sugerencia de categoría de falla</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" s="27" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M31" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N31" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q31" s="26" t="inlineStr">
+        <is>
+          <t>Correctivo muestra sugerencia ML si FastAPI responde</t>
+        </is>
+      </c>
+      <c r="R31" s="26" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/</t>
+        </is>
+      </c>
+      <c r="S31" s="26" t="inlineStr">
+        <is>
+          <t>MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="T31" s="26" t="inlineStr">
+        <is>
+          <t>src/features/mantenimiento/components/MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="U31" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/src/features/mantenimiento/components/MantenimientoForm.jsx</t>
+        </is>
+      </c>
+      <c r="V31" s="27" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (ML-004)</t>
+        </is>
+      </c>
+      <c r="X31" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y31" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z31" s="26" t="inlineStr">
+        <is>
+          <t>HU-MNT-009 / HU-ML-004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="14">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>F-031</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Indicadores operativos</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" s="25" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>GET /dashboard pinta conteos persistidos tras el login</t>
+        </is>
+      </c>
+      <c r="R32" s="22" t="inlineStr">
+        <is>
+          <t>src/features/dashboard/components/</t>
+        </is>
+      </c>
+      <c r="S32" s="22" t="inlineStr">
+        <is>
+          <t>DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="T32" s="22" t="inlineStr">
+        <is>
+          <t>src/features/dashboard/components/DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="U32" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/features/dashboard/components/DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="V32" s="25" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+      <c r="W32" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (DSH-001)</t>
+        </is>
+      </c>
+      <c r="X32" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y32" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z32" s="22" t="inlineStr">
+        <is>
+          <t>HU-DSH-001–004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="14">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>F-032</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Alertas predictivas</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="27" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N33" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q33" s="26" t="inlineStr">
+        <is>
+          <t>GET /ml/alertas lista top de riesgo; vacío/N/A si ML caído</t>
+        </is>
+      </c>
+      <c r="R33" s="26" t="inlineStr">
+        <is>
+          <t>src/features/dashboard/components/</t>
+        </is>
+      </c>
+      <c r="S33" s="26" t="inlineStr">
+        <is>
+          <t>DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="T33" s="26" t="inlineStr">
+        <is>
+          <t>src/features/dashboard/components/DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="U33" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/src/features/dashboard/components/DashboardPage.jsx</t>
+        </is>
+      </c>
+      <c r="V33" s="27" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (ML-001)</t>
+        </is>
+      </c>
+      <c r="X33" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y33" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z33" s="26" t="inlineStr">
+        <is>
+          <t>HU-ML-001 / HU-ML-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="14">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>F-033</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Consulta de equipos por etiquetas</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" s="25" t="inlineStr">
+        <is>
+          <t>I-008</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q34" s="22" t="inlineStr">
+        <is>
+          <t>GET /dashboard/consulta filtra tipo, estado y tipo_otro</t>
+        </is>
+      </c>
+      <c r="R34" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S34" s="22" t="inlineStr">
+        <is>
+          <t>DashboardController.php</t>
+        </is>
+      </c>
+      <c r="T34" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/DashboardController.php</t>
+        </is>
+      </c>
+      <c r="U34" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/DashboardController.php</t>
+        </is>
+      </c>
+      <c r="V34" s="25" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W34" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/DashboardConsultaTest.php</t>
+        </is>
+      </c>
+      <c r="X34" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y34" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z34" s="22" t="inlineStr">
+        <is>
+          <t>HU-DSH-005 / HU-DSH-006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="14">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>F-034</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Predicción de riesgo (un equipo)</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>ML (FastAPI)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" s="27" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N35" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q35" s="26" t="inlineStr">
+        <is>
+          <t>POST /predict/riesgo devuelve score; proxy JWT /api/v2/ml/*</t>
+        </is>
+      </c>
+      <c r="R35" s="26" t="inlineStr">
+        <is>
+          <t>ml/app/</t>
+        </is>
+      </c>
+      <c r="S35" s="26" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="T35" s="26" t="inlineStr">
+        <is>
+          <t>ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="U35" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="V35" s="27" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="inlineStr">
+        <is>
+          <t>ml/tests/test_ml_schemas.py</t>
+        </is>
+      </c>
+      <c r="X35" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y35" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z35" s="26" t="inlineStr">
+        <is>
+          <t>HU-ML-002.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="14">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>F-035</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Predicción de riesgo (lote)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>ML (FastAPI)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" s="25" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O36" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>Batch JSON {} (no []); límite acotado</t>
+        </is>
+      </c>
+      <c r="R36" s="22" t="inlineStr">
+        <is>
+          <t>ml/app/</t>
+        </is>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="T36" s="22" t="inlineStr">
+        <is>
+          <t>ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="U36" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="V36" s="25" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W36" s="22" t="inlineStr">
+        <is>
+          <t>ml/tests/test_ml_schemas.py</t>
+        </is>
+      </c>
+      <c r="X36" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y36" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z36" s="22" t="inlineStr">
+        <is>
+          <t>HU-INV-006. iter ≥2 (batch [] vs {}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="14">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>F-036</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Degradación si FastAPI no responde</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" s="27" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M37" s="26" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N37" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O37" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P37" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q37" s="26" t="inlineStr">
+        <is>
+          <t>Inventario y login siguen; alertas N/A (ADR-002)</t>
+        </is>
+      </c>
+      <c r="R37" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S37" s="26" t="inlineStr">
+        <is>
+          <t>MlController.php</t>
+        </is>
+      </c>
+      <c r="T37" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/MlController.php</t>
+        </is>
+      </c>
+      <c r="U37" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/backend/api/v2/controllers/MlController.php</t>
+        </is>
+      </c>
+      <c r="V37" s="27" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (ML-003 / DEG-001)</t>
+        </is>
+      </c>
+      <c r="X37" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y37" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z37" s="26" t="inlineStr">
+        <is>
+          <t>HU-ML-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="14">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>F-037</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Reentrenamiento del modelo</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>ML (FastAPI)</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" s="25" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q38" s="22" t="inlineStr">
+        <is>
+          <t>POST /ml/train (Admin); artefacto riesgo_equipo_v2.joblib</t>
+        </is>
+      </c>
+      <c r="R38" s="22" t="inlineStr">
+        <is>
+          <t>ml/app/</t>
+        </is>
+      </c>
+      <c r="S38" s="22" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="T38" s="22" t="inlineStr">
+        <is>
+          <t>ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="U38" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/ml/app/main.py</t>
+        </is>
+      </c>
+      <c r="V38" s="25" t="inlineStr">
+        <is>
+          <t>e9a0965</t>
+        </is>
+      </c>
+      <c r="W38" s="22" t="inlineStr">
+        <is>
+          <t>ml/tests/test_features.py</t>
+        </is>
+      </c>
+      <c r="X38" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y38" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z38" s="22" t="inlineStr">
+        <is>
+          <t>HU-ML-003. Features telemetría I-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="14">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>F-038</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>reportes</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>PDF de ficha de equipo</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" s="27" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="M39" s="26" t="inlineStr">
+        <is>
+          <t>Zero-shot + few-shot</t>
+        </is>
+      </c>
+      <c r="N39" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q39" s="26" t="inlineStr">
+        <is>
+          <t>GET /reportes/equipo/{id} genera PDF con código patrimonial</t>
+        </is>
+      </c>
+      <c r="R39" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S39" s="26" t="inlineStr">
+        <is>
+          <t>ReporteController.php</t>
+        </is>
+      </c>
+      <c r="T39" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="U39" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="V39" s="27" t="inlineStr">
+        <is>
+          <t>f086a63</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (RPT-001)</t>
+        </is>
+      </c>
+      <c r="X39" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y39" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z39" s="26" t="inlineStr">
+        <is>
+          <t>HU-RPT-001 / HU-FIC-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="14">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>F-039</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>reportes</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>PDF de historial de mantenimiento</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" s="25" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="M40" s="22" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="N6" s="22" t="inlineStr">
+      <c r="N40" s="22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O6" s="22" t="n">
+      <c r="O40" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="P40" s="22" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
-        <is>
-          <t>Timeline, registro estructurado y sync de telemetría post-mantenimiento</t>
-        </is>
-      </c>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="Q40" s="22" t="inlineStr">
+        <is>
+          <t>GET /reportes/mantenimiento/historial/{codigo} descarga PDF</t>
+        </is>
+      </c>
+      <c r="R40" s="22" t="inlineStr">
         <is>
           <t>backend/api/v2/controllers/</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
-        <is>
-          <t>MantenimientoController.php</t>
-        </is>
-      </c>
-      <c r="T6" s="22" t="inlineStr">
-        <is>
-          <t>backend/api/v2/controllers/MantenimientoController.php</t>
-        </is>
-      </c>
-      <c r="U6" s="26" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/MantenimientoController.php</t>
-        </is>
-      </c>
-      <c r="V6" s="26" t="inlineStr">
+      <c r="S40" s="22" t="inlineStr">
+        <is>
+          <t>ReporteController.php</t>
+        </is>
+      </c>
+      <c r="T40" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="U40" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="V40" s="25" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
-      <c r="W6" s="22" t="inlineStr">
-        <is>
-          <t>backend/tests/MantenimientoTest.php</t>
-        </is>
-      </c>
-      <c r="X6" s="22" t="inlineStr">
+      <c r="W40" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (RPT-002)</t>
+        </is>
+      </c>
+      <c r="X40" s="22" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y6" s="22" t="inlineStr">
+      <c r="Y40" s="22" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z6" s="22" t="inlineStr">
-        <is>
-          <t>SHA de timeline/categoría: 8b20337 [I-003]. Sync de telemetría: I-008. PHPUnit: sync de telemetría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" s="14">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>F-006</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>dashboard</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>Indicadores operativos y consulta de equipos por etiquetas</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="Z40" s="22" t="inlineStr">
+        <is>
+          <t>HU-RPT-002 / HU-MNT-005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="14">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>F-040</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>reportes</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>PDF de detalle de intervención</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" s="27" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="M41" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N41" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q41" s="26" t="inlineStr">
+        <is>
+          <t>GET /reportes/mantenimiento/{id} descarga PDF de la ficha</t>
+        </is>
+      </c>
+      <c r="R41" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S41" s="26" t="inlineStr">
+        <is>
+          <t>ReporteController.php</t>
+        </is>
+      </c>
+      <c r="T41" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="U41" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/8b20337/backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="V41" s="27" t="inlineStr">
+        <is>
+          <t>8b20337</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (RPT-003)</t>
+        </is>
+      </c>
+      <c r="X41" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y41" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z41" s="26" t="inlineStr">
+        <is>
+          <t>HU-RPT-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="14">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>F-041</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>reportes</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Descarga PDF autenticada (JWT)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>Presentation (React)</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" s="25" t="inlineStr">
+        <is>
+          <t>I-006</t>
+        </is>
+      </c>
+      <c r="M42" s="22" t="inlineStr">
+        <is>
+          <t>CoT guiado</t>
+        </is>
+      </c>
+      <c r="N42" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O42" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q42" s="22" t="inlineStr">
+        <is>
+          <t>downloadPdf usa blob + Authorization; no window.open anónimo</t>
+        </is>
+      </c>
+      <c r="R42" s="22" t="inlineStr">
+        <is>
+          <t>src/lib/</t>
+        </is>
+      </c>
+      <c r="S42" s="22" t="inlineStr">
+        <is>
+          <t>api.js</t>
+        </is>
+      </c>
+      <c r="T42" s="22" t="inlineStr">
+        <is>
+          <t>src/lib/api.js</t>
+        </is>
+      </c>
+      <c r="U42" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/lib/api.js</t>
+        </is>
+      </c>
+      <c r="V42" s="25" t="inlineStr">
+        <is>
+          <t>5ce7575</t>
+        </is>
+      </c>
+      <c r="W42" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (RPT-004)</t>
+        </is>
+      </c>
+      <c r="X42" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y42" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z42" s="22" t="inlineStr">
+        <is>
+          <t>HU-RPT-004. iter blob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="14">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>F-042</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>reportes</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>PDF de cronograma (matriz A4)</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" s="27" t="inlineStr">
+        <is>
+          <t>I-016</t>
+        </is>
+      </c>
+      <c r="M43" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N43" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q43" s="26" t="inlineStr">
+        <is>
+          <t>GET /reportes/cronograma/{id} A4 L–V, 2 meses/hoja, Xn y HORA PROGRAMADA con borde</t>
+        </is>
+      </c>
+      <c r="R43" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S43" s="26" t="inlineStr">
+        <is>
+          <t>ReporteController.php</t>
+        </is>
+      </c>
+      <c r="T43" s="26" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="U43" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/controllers/ReporteController.php</t>
+        </is>
+      </c>
+      <c r="V43" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X43" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y43" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z43" s="26" t="inlineStr">
+        <is>
+          <t>HU-CRN-004. Cadena I-012…I-016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="14">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>F-043</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Menú e historial de cronogramas</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" s="25" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q44" s="22" t="inlineStr">
+        <is>
+          <t>Navbar «Cronograma»; GET /cronogramas lista planes (varios por año)</t>
+        </is>
+      </c>
+      <c r="R44" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S44" s="22" t="inlineStr">
+        <is>
+          <t>CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="T44" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="U44" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="V44" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W44" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CRN-001 / CRN-008)</t>
+        </is>
+      </c>
+      <c r="X44" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y44" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z44" s="22" t="inlineStr">
+        <is>
+          <t>HU-CRN-007 / HU-CRN-008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="14">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>F-044</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Alta de cronograma</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" s="27" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="M45" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N45" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q45" s="26" t="inlineStr">
+        <is>
+          <t>POST /cronogramas {anio, nombre} crea documento; practicante 403</t>
+        </is>
+      </c>
+      <c r="R45" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S45" s="26" t="inlineStr">
+        <is>
+          <t>CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="T45" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="U45" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaListPage.jsx</t>
+        </is>
+      </c>
+      <c r="V45" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X45" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y45" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z45" s="26" t="inlineStr">
+        <is>
+          <t>HU-CRN-009.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="14">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>F-045</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Marcado Xn por día</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" s="25" t="inlineStr">
+        <is>
+          <t>I-014</t>
+        </is>
+      </c>
+      <c r="M46" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N46" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q46" s="22" t="inlineStr">
+        <is>
+          <t>POST celdas {cantidad}; una columna/día; selector X1…Xn (PC+laptop)</t>
+        </is>
+      </c>
+      <c r="R46" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S46" s="22" t="inlineStr">
+        <is>
+          <t>CronogramaCantidadPopover.jsx</t>
+        </is>
+      </c>
+      <c r="T46" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaCantidadPopover.jsx</t>
+        </is>
+      </c>
+      <c r="U46" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaCantidadPopover.jsx</t>
+        </is>
+      </c>
+      <c r="V46" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W46" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/utils/cronogramaUtils.test.js</t>
+        </is>
+      </c>
+      <c r="X46" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y46" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z46" s="22" t="inlineStr">
+        <is>
+          <t>HU-CRN-001–003 / HU-CRN-013. No turnos mañana/tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="14">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>F-046</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Liberar o cambiar cantidad</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>Alto (integración/validación)</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" s="27" t="inlineStr">
+        <is>
+          <t>I-014</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N47" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q47" s="26" t="inlineStr">
+        <is>
+          <t>cantidad 0 o DELETE de celda libera el asiento</t>
+        </is>
+      </c>
+      <c r="R47" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S47" s="26" t="inlineStr">
+        <is>
+          <t>CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="T47" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="U47" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="V47" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CRN-003)</t>
+        </is>
+      </c>
+      <c r="X47" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y47" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z47" s="26" t="inlineStr">
+        <is>
+          <t>HU-CRN-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="14">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>F-047</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Totales de equipos en matriz</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
         <is>
           <t>Medio (entrega/despliegue)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G48" s="24" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" s="25" t="inlineStr">
+        <is>
+          <t>I-011</t>
+        </is>
+      </c>
+      <c r="M48" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N48" s="22" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="22" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q48" s="22" t="inlineStr">
+        <is>
+          <t>Columna Tot, pie Subtotal PC/Lap/Imp y Total equipos</t>
+        </is>
+      </c>
+      <c r="R48" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S48" s="22" t="inlineStr">
+        <is>
+          <t>CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="T48" s="22" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="U48" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="V48" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W48" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CRN-010)</t>
+        </is>
+      </c>
+      <c r="X48" s="22" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y48" s="22" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z48" s="22" t="inlineStr">
+        <is>
+          <t>HU-CRN-010.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="14">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>F-048</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Personal en HORA PROGRAMADA</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" s="27" t="inlineStr">
+        <is>
+          <t>I-013</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N49" s="26" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="O49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="26" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="Q49" s="26" t="inlineStr">
+        <is>
+          <t>PUT /cronogramas/{id}/personal; recuadro de personas (no bienes)</t>
+        </is>
+      </c>
+      <c r="R49" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S49" s="26" t="inlineStr">
+        <is>
+          <t>CronogramaPersonalPanel.jsx</t>
+        </is>
+      </c>
+      <c r="T49" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaPersonalPanel.jsx</t>
+        </is>
+      </c>
+      <c r="U49" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaPersonalPanel.jsx</t>
+        </is>
+      </c>
+      <c r="V49" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CRN-012)</t>
+        </is>
+      </c>
+      <c r="X49" s="26" t="inlineStr">
+        <is>
+          <t>AxlTech25</t>
+        </is>
+      </c>
+      <c r="Y49" s="26" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="Z49" s="26" t="inlineStr">
+        <is>
+          <t>HU-CRN-011 residual horarios; I-013 personas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="14">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>F-049</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Baja de cronograma</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>API (PHP)</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L7" s="28" t="inlineStr">
-        <is>
-          <t>I-006</t>
-        </is>
-      </c>
-      <c r="M7" s="27" t="inlineStr">
-        <is>
-          <t>CoT guiado</t>
-        </is>
-      </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" s="25" t="inlineStr">
+        <is>
+          <t>I-015</t>
+        </is>
+      </c>
+      <c r="M50" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N50" s="22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O7" s="27" t="n">
+      <c r="O50" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="P50" s="22" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q7" s="27" t="inlineStr">
-        <is>
-          <t>Dashboard de métricas, alertas ML y panel de consulta con filtros</t>
-        </is>
-      </c>
-      <c r="R7" s="27" t="inlineStr">
-        <is>
-          <t>src/features/dashboard/</t>
-        </is>
-      </c>
-      <c r="S7" s="27" t="inlineStr">
-        <is>
-          <t>DashboardPage.jsx</t>
-        </is>
-      </c>
-      <c r="T7" s="27" t="inlineStr">
-        <is>
-          <t>src/features/dashboard/components/DashboardPage.jsx</t>
-        </is>
-      </c>
-      <c r="U7" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/5ce7575/src/features/dashboard/components/DashboardPage.jsx</t>
-        </is>
-      </c>
-      <c r="V7" s="28" t="inlineStr">
-        <is>
-          <t>5ce7575</t>
-        </is>
-      </c>
-      <c r="W7" s="27" t="inlineStr">
-        <is>
-          <t>backend/tests/DashboardConsultaTest.php</t>
-        </is>
-      </c>
-      <c r="X7" s="27" t="inlineStr">
+      <c r="Q50" s="22" t="inlineStr">
+        <is>
+          <t>DELETE /cronogramas/{id} CASCADE; practicante 403</t>
+        </is>
+      </c>
+      <c r="R50" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/</t>
+        </is>
+      </c>
+      <c r="S50" s="22" t="inlineStr">
+        <is>
+          <t>CronogramaController.php</t>
+        </is>
+      </c>
+      <c r="T50" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/controllers/CronogramaController.php</t>
+        </is>
+      </c>
+      <c r="U50" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/controllers/CronogramaController.php</t>
+        </is>
+      </c>
+      <c r="V50" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W50" s="22" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X50" s="22" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y7" s="27" t="inlineStr">
+      <c r="Y50" s="22" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z7" s="27" t="inlineStr">
-        <is>
-          <t>Commit 5ce7575 [I-006] (dashboard de métricas + JWT). Alertas ML: I-007. Consulta tipo_otro: I-008.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" s="14">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>F-007</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Riesgo predictivo, lote, categoría de falla y reentrenamiento</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="Z50" s="22" t="inlineStr">
+        <is>
+          <t>HU-CRN-014.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="14">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>F-050</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Bandas de gerencia</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>ML (FastAPI)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Alto (integración/validación)</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>Presentation (React)</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Medio (entrega/despliegue)</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="inlineStr">
-        <is>
-          <t>I-007</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="inlineStr">
-        <is>
-          <t>CoT guiado</t>
-        </is>
-      </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" s="27" t="inlineStr">
+        <is>
+          <t>I-017</t>
+        </is>
+      </c>
+      <c r="M51" s="26" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N51" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O8" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="O51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="inlineStr">
-        <is>
-          <t>Microservicio FastAPI + proxy PHP /api/v2/ml/* + badges de riesgo en UI</t>
-        </is>
-      </c>
-      <c r="R8" s="22" t="inlineStr">
-        <is>
-          <t>ml/app/</t>
-        </is>
-      </c>
-      <c r="S8" s="22" t="inlineStr">
-        <is>
-          <t>main.py</t>
-        </is>
-      </c>
-      <c r="T8" s="22" t="inlineStr">
-        <is>
-          <t>ml/app/main.py</t>
-        </is>
-      </c>
-      <c r="U8" s="26" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/e9a0965/ml/app/main.py</t>
-        </is>
-      </c>
-      <c r="V8" s="26" t="inlineStr">
-        <is>
-          <t>e9a0965</t>
-        </is>
-      </c>
-      <c r="W8" s="22" t="inlineStr">
-        <is>
-          <t>ml/tests/test_features.py</t>
-        </is>
-      </c>
-      <c r="X8" s="22" t="inlineStr">
+      <c r="Q51" s="26" t="inlineStr">
+        <is>
+          <t>Matriz y PDF agrupan áreas bajo fila banda (sin Xn)</t>
+        </is>
+      </c>
+      <c r="R51" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/</t>
+        </is>
+      </c>
+      <c r="S51" s="26" t="inlineStr">
+        <is>
+          <t>CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="T51" s="26" t="inlineStr">
+        <is>
+          <t>src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="U51" s="27" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
+        </is>
+      </c>
+      <c r="V51" s="27" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="inlineStr">
+        <is>
+          <t>backend/tests/CronogramaTest.php</t>
+        </is>
+      </c>
+      <c r="X51" s="26" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y8" s="22" t="inlineStr">
+      <c r="Y51" s="26" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z8" s="22" t="inlineStr">
-        <is>
-          <t>Commit e9a0965 [I-007] (FastAPI). Telemetría/ficha predictiva: I-008. pytest: test_features.py y test_ml_schemas.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" s="14">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>F-008</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>reportes</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>Reportes PDF de ficha, mantenimiento y cronograma</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="Z51" s="26" t="inlineStr">
+        <is>
+          <t>HU-CRN-015. Sin asignaciones no hay bandas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="14">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>F-051</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>cronograma</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Cobertura del mínimo anual</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>API (PHP)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F52" s="24" t="inlineStr">
         <is>
           <t>Medio (entrega/despliegue)</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G52" s="24" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L9" s="28" t="inlineStr">
-        <is>
-          <t>I-004</t>
-        </is>
-      </c>
-      <c r="M9" s="27" t="inlineStr">
-        <is>
-          <t>Zero-shot + few-shot</t>
-        </is>
-      </c>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" s="25" t="inlineStr">
+        <is>
+          <t>I-010</t>
+        </is>
+      </c>
+      <c r="M52" s="22" t="inlineStr">
+        <is>
+          <t>Few-shot</t>
+        </is>
+      </c>
+      <c r="N52" s="22" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="O9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="27" t="inlineStr">
+      <c r="O52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="22" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="Q9" s="27" t="inlineStr">
-        <is>
-          <t>PDF de ficha, historial de mantenimiento y matriz de cronograma (A4 L–V) con JWT</t>
-        </is>
-      </c>
-      <c r="R9" s="27" t="inlineStr">
-        <is>
-          <t>backend/api/v2/controllers/</t>
-        </is>
-      </c>
-      <c r="S9" s="27" t="inlineStr">
-        <is>
-          <t>ReporteController.php</t>
-        </is>
-      </c>
-      <c r="T9" s="27" t="inlineStr">
-        <is>
-          <t>backend/api/v2/controllers/ReporteController.php</t>
-        </is>
-      </c>
-      <c r="U9" s="28" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/f086a63/backend/api/v2/controllers/ReporteController.php</t>
-        </is>
-      </c>
-      <c r="V9" s="28" t="inlineStr">
-        <is>
-          <t>f086a63</t>
-        </is>
-      </c>
-      <c r="W9" s="27" t="inlineStr">
-        <is>
-          <t>backend/tests/CronogramaTest.php</t>
-        </is>
-      </c>
-      <c r="X9" s="27" t="inlineStr">
+      <c r="Q52" s="22" t="inlineStr">
+        <is>
+          <t>GET matriz/cobertura: áreas cuya suma Xn no cubre PC+laptop</t>
+        </is>
+      </c>
+      <c r="R52" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/</t>
+        </is>
+      </c>
+      <c r="S52" s="22" t="inlineStr">
+        <is>
+          <t>Cronograma.php</t>
+        </is>
+      </c>
+      <c r="T52" s="22" t="inlineStr">
+        <is>
+          <t>backend/api/v2/models/Cronograma.php</t>
+        </is>
+      </c>
+      <c r="U52" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/backend/api/v2/models/Cronograma.php</t>
+        </is>
+      </c>
+      <c r="V52" s="25" t="inlineStr">
+        <is>
+          <t>3394712</t>
+        </is>
+      </c>
+      <c r="W52" s="22" t="inlineStr">
+        <is>
+          <t>documents/04_testing/plan_pruebas_funcionales.md (CRN-006)</t>
+        </is>
+      </c>
+      <c r="X52" s="22" t="inlineStr">
         <is>
           <t>AxlTech25</t>
         </is>
       </c>
-      <c r="Y9" s="27" t="inlineStr">
+      <c r="Y52" s="22" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="Z9" s="27" t="inlineStr">
-        <is>
-          <t>SHA origen ficha: f086a63 [I-004]. Descarga JWT: 5ce7575 [I-006]. PDF cronograma (matriz papel A4): I-012…I-016 (3394712).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" s="14">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>F-009</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>cronograma</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>Cronograma anual de preventivo (historial, matriz Xn, PDF, gerencias)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>Presentation (React)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Alto (integración/validación)</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="inlineStr">
-        <is>
-          <t>I-010</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="inlineStr">
-        <is>
-          <t>Few-shot</t>
-        </is>
-      </c>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P10" s="22" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="Q10" s="22" t="inlineStr">
-        <is>
-          <t>Historial de planes, matriz área×día×cantidad, personal, PDF A4 y bandas de gerencia</t>
-        </is>
-      </c>
-      <c r="R10" s="22" t="inlineStr">
-        <is>
-          <t>src/features/cronograma/</t>
-        </is>
-      </c>
-      <c r="S10" s="22" t="inlineStr">
-        <is>
-          <t>CronogramaMatrizPage.jsx</t>
-        </is>
-      </c>
-      <c r="T10" s="22" t="inlineStr">
-        <is>
-          <t>src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
-        </is>
-      </c>
-      <c r="U10" s="26" t="inlineStr">
-        <is>
-          <t>https://github.com/AxlTech25/Gestion-MPA/blob/3394712/src/features/cronograma/components/CronogramaMatrizPage.jsx</t>
-        </is>
-      </c>
-      <c r="V10" s="26" t="inlineStr">
-        <is>
-          <t>3394712</t>
-        </is>
-      </c>
-      <c r="W10" s="22" t="inlineStr">
-        <is>
-          <t>backend/tests/CronogramaTest.php</t>
-        </is>
-      </c>
-      <c r="X10" s="22" t="inlineStr">
-        <is>
-          <t>AxlTech25</t>
-        </is>
-      </c>
-      <c r="Y10" s="22" t="inlineStr">
-        <is>
-          <t>Desarrollador</t>
-        </is>
-      </c>
-      <c r="Z10" s="22" t="inlineStr">
-        <is>
-          <t>Incremento 8 cerrado 2026-09-17 (0.10.0–0.10.7). Origen I-010; parches I-011…I-017. SHA: 3394712. También cronogramaUtils.test.js. API: CronogramaController.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="29" customHeight="1" s="14"/>
-    <row r="12" ht="29" customHeight="1" s="14"/>
-    <row r="13" ht="29" customHeight="1" s="14"/>
-    <row r="14" ht="29" customHeight="1" s="14"/>
-    <row r="15" ht="29" customHeight="1" s="14"/>
-    <row r="16" ht="29" customHeight="1" s="14"/>
-    <row r="17" ht="29" customHeight="1" s="14"/>
-    <row r="18" ht="29" customHeight="1" s="14"/>
-    <row r="20" ht="29" customHeight="1" s="14"/>
+      <c r="Z52" s="22" t="inlineStr">
+        <is>
+          <t>HU-CRN-005 / HU-CRN-006. SIGA/SAF = área.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z10"/>
+  <autoFilter ref="A1:Z52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId2"/>
@@ -2299,6 +7750,132 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V52" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2382,14 +7959,14 @@
       </c>
     </row>
     <row r="2" ht="90" customHeight="1" s="14">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>F-001</t>
+          <t>F-001, F-002, F-003, F-004, F-031, F-041</t>
         </is>
       </c>
       <c r="C2" s="22" t="inlineStr">
@@ -2430,76 +8007,76 @@
           <t>Login JWT funcional (AuthContext, PrivateRoute, middleware)</t>
         </is>
       </c>
-      <c r="K2" s="26" t="inlineStr">
+      <c r="K2" s="25" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1" s="14">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>I-005</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>F-002</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>F-006, F-007, F-010, F-011</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React. Contexto: áreas y responsables no deben estar hardcodeados en EquipoForm; tablas v2_areas y v2_usuarios existen; ruta /v2/configuracion; roles Administrador, Tecnico, Practicante. Objetivo: CRUD de áreas y alta/listado de personal. Tarea: modelos PDO; password_hash BCRYPT; rutas /areas y /usuarios; ConfiguracionPage (pestañas); EquipoForm consume áreas desde API. Restricciones: no MD5; no requireRole en este incremento (deuda → I-009). Criterios: crear un área y verla en EquipoForm; usuario con hash en BD.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F3" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>La API de usuarios quedó solo autenticada. I-009 añade requireRole Administrador.</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
+      <c r="I3" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="J3" s="26" t="inlineStr">
         <is>
           <t>Áreas y personal funcionales; EquipoForm dinámico</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
         <is>
           <t>4e08b9e</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1" s="14">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>I-002</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>F-003</t>
+          <t>F-014, F-015, F-016, F-019</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
@@ -2540,76 +8117,76 @@
           <t>CRUD de equipos con código de 12 dígitos y RAM numérica</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1" s="14">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>F-004</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>F-021, F-022, F-023</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React; replica el patrón I-002. Contexto: equipos ya se listan; hace falta consultar/editar ficha técnica del equipo. Tarea: modelo/controlador/ruta de fichas; GET por id y por código patrimonial; acceso desde inventario (modal o /v2/ficha-tecnica). Restricciones: no PDF (I-004); no bloque ML (I-008). Criterios: GET ficha existente o vacío controlado (no 500).</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>N/A — evaluación predictiva en ficha es I-008.</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>API y UI de ficha técnica por id o código</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" s="14">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>I-003</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>F-005</t>
+          <t>F-025, F-026, F-027, F-028</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -2650,76 +8227,76 @@
           <t>Timeline y alta estructurada de mantenimientos</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" s="14">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>I-006</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>F-006</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>F-031</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP/React (mismo incremento 0.6.0 que F-001). Objetivo: métricas operativas en GET /api/v2/dashboard y UI DashboardPage (conteos, no ML). Tarea: DashboardController + DashboardPage; no badges de riesgo (I-007); no panel de consulta por etiquetas (I-008). Restricciones: no llamar a :8000. Criterios: dashboard muestra conteos persistidos tras login.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>CoT guiado</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>N/A — consulta tipo_otro es I-008; alertas ML son I-007.</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Dashboard de métricas operativas funcional</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>5ce7575</t>
         </is>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" s="14">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>I-007</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>F-007</t>
+          <t>F-020, F-030, F-032, F-034, F-035, F-036, F-037</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -2760,76 +8337,76 @@
           <t>FastAPI + proxy PHP + badges; degradación controlada</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t>e9a0965</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" s="14">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>I-004</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>F-008</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>F-017, F-038, F-039, F-040</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP (dompdf) y React. Contexto: inventario y ficha ya existen. Objetivo: GET /api/v2/reportes/equipo/{id} genera PDF; InventarioPage filtra en cliente y ofrece descargar ficha. Tarea: Composer dompdf; ReporteController HTML→PDF; botón en la fila. Restricciones: PDF binario, no base64; no reportes de mantenimiento en este incremento. Criterios: PDF muestra código patrimonial; filtro de texto reduce filas.</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Zero-shot + few-shot</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>window.open sin token; I-006 cambia la descarga a blob + Authorization.</t>
         </is>
       </c>
-      <c r="H9" s="27" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>PDF de ficha y filtros de inventario funcionales</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t>f086a63</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" s="14">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>I-008</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>F-003, F-005, F-006, F-007</t>
+          <t>F-024, F-029, F-033</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2870,76 +8447,76 @@
           <t>Telemetría, sync, ficha predictiva y consulta de equipos</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" s="14">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>I-009</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>F-001, F-002, F-003</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>F-005, F-012, F-018</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior de API PHP y React. Contexto: 0.9.1; JWT existe; un Técnico puede mutar /usuarios; plantilla Excel desalinea numero_serie/area por falta de color. Objetivo: requireRole Administrador en escritura de usuarios; no autoeliminación ni borrar el último admin; RoleRoute en Configuración; fila ejemplo Excel alineada. Criterios: Técnico en POST /usuarios → 403.</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>CoT guiado</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>I-005 no puso autorización en servidor (deuda de RBAC).</t>
         </is>
       </c>
-      <c r="H11" s="27" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="J11" s="26" t="inlineStr">
         <is>
           <t>requireRole en /usuarios y plantilla Excel alineada</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t>8b20337</t>
         </is>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" s="14">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>I-010</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>F-009</t>
+          <t>F-043, F-044, F-051</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2980,76 +8557,76 @@
           <t>Historial, matriz y PDF autenticado (0.10.0)</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" s="14">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>I-011</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>F-009</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>F-047</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: 0.10.0. Faltan subtotal/total; hay que programar hora de cada equipo; Imprimir PDF abre pestaña en blanco. Objetivo: parche 0.10.1. El asiento sigue área+fecha+turno (ADR-003). Tarea: columna Tot y pie Subtotal/Total; v2_cronograma_horarios + modal PUT; downloadPdf con attachment y Content-Type PDF. Criterios: pie de totales; modal horas; PDF descarga archivo.</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>I-010 no tenía totales ni horas por equipo; downloadPdf sin attachment.</t>
         </is>
       </c>
-      <c r="H13" s="27" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="J13" s="26" t="inlineStr">
         <is>
           <t>Totales, horarios por equipo e impresión con download</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1" s="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>I-012</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>F-008, F-009</t>
+          <t>F-042</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -3090,76 +8667,76 @@
           <t>PDF tipo matriz (papel 2024)</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1" s="14">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>I-013</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>F-009</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>F-048</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: el recuadro HORA PROGRAMADA del papel son las personas que hacen el preventivo, no los bienes del área. Objetivo: recuadro editable en matriz y PDF. Tarea: v2_cronograma_personal; PUT /cronogramas/{id}/personal; quitar del PDF la tabla grande de horas por CPU. Criterios: se edita el nombre y se ve igual en el PDF.</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="27" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>I-012 listaba PCs del inventario en HORA PROGRAMADA; el papel lista personas.</t>
         </is>
       </c>
-      <c r="H15" s="27" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="J15" s="26" t="inlineStr">
         <is>
           <t>Personal del preventivo en HORA PROGRAMADA</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1" s="14">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>I-014</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>F-009</t>
+          <t>F-045, F-046</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -3200,76 +8777,76 @@
           <t>Xn = cantidad por día (no turnos)</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="17" ht="90" customHeight="1" s="14">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>I-015</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>F-009</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>F-049</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP 8 / React 19 / Dompdf. Contexto: PDF A3 4 meses con sábados/domingos; hace falta A4, L–V, 2 meses/hoja, año del documento y poder borrar un plan. Objetivo: PDF A4 apaisado laborable; DELETE /cronogramas/{id} CASCADE; matriz UI sin fines de semana. Restricciones: no auto-fill; Practicante no elimina; conservar N°/área/conteos.</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>I-012 era A3 calendario completo; el responsable pidió A4 laborable y baja.</t>
         </is>
       </c>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J17" s="26" t="inlineStr">
         <is>
           <t>PDF A4 L–V 2 meses/hoja y DELETE del plan</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1" s="14">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>I-016</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>F-008, F-009</t>
+          <t>F-042</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -3310,62 +8887,62 @@
           <t>PDF encajado; HORA PROGRAMADA con borde</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="K18" s="25" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
       </c>
     </row>
     <row r="19" ht="90" customHeight="1" s="14">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>I-017</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>F-002, F-009</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>F-008, F-009, F-013, F-050</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Actúa como desarrollador senior PHP 8 / React 19. Contexto: el papel agrupa áreas bajo filas de gerencia; v2_areas solo tenía alta. Objetivo: catálogo v2_gerencias; área.gerencia_id; CRUD de área (Admin); matriz y PDF con fila banda. Restricciones: no auto-fill; SIGA/SAF son áreas, no gerencias; no borrar área con equipos (409); no etiqueta libre. Criterios: asignar gerencia; 409 si hay equipos; bandas en cronograma/PDF.</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Few-shot</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>Cierre del Incremento 8: gerencias del papel y CRUD de áreas pendiente desde I-005.</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>Gerencias, CRUD de áreas y bandas en cronograma (0.10.7)</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr">
+      <c r="K19" s="27" t="inlineStr">
         <is>
           <t>3394712</t>
         </is>
@@ -3640,7 +9217,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Identificador del prompt vigente (I-002…I-017). Una fila por función F-001…F-009 en Prompts Detallados, más refinamientos. Hipervínculo al markdown en GitHub (prompts/).</t>
+          <t>Identificador del prompt vigente (I-002…I-017). Varias funciones F-00N pueden compartir un I-* (el prompt generó más de un componente). Hipervínculo al markdown en GitHub (prompts/).</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
